--- a/docs/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -40,11 +40,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[m]:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="[hh]:mm:ss"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1280,7 +1281,7 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -1806,6 +1807,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2207,7 +2209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE49"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="42.83203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2449,4297 +2451,4358 @@
       </c>
     </row>
     <row r="3" ht="22" customFormat="1" customHeight="1" s="163">
-      <c r="A3" s="158" t="inlineStr">
-        <is>
-          <t>Angel From Montgomery</t>
-        </is>
-      </c>
-      <c r="B3" s="159" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C3" s="159" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D3" s="158" t="inlineStr">
-        <is>
-          <t>John Prine</t>
-        </is>
-      </c>
-      <c r="E3" s="158" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>All These Things That I've Done</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The Killers</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F3" s="160" t="n">
-        <v>0.002766203703703704</v>
-      </c>
-      <c r="G3" s="158" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H3" s="158" t="n"/>
-      <c r="I3" s="158" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J3" s="158" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K3" s="158" t="n"/>
-      <c r="L3" s="161">
+      <c r="F3" s="201" t="n">
+        <v>0.003483796296296296</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L3">
         <f>COUNTIF(M3:AV3,"✓")</f>
         <v/>
       </c>
-      <c r="M3" s="161" t="n"/>
-      <c r="N3" s="161" t="n"/>
-      <c r="O3" s="162" t="n"/>
-      <c r="P3" s="158" t="n"/>
-      <c r="Q3" s="158" t="n"/>
-      <c r="R3" s="158" t="n"/>
-      <c r="S3" s="158" t="n"/>
-      <c r="T3" s="158" t="n"/>
-      <c r="U3" s="158" t="n"/>
-      <c r="V3" s="158" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W3" s="158" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X3" s="158" t="n"/>
-      <c r="Y3" s="158" t="n"/>
-      <c r="Z3" s="158" t="n"/>
-      <c r="AA3" s="158" t="n"/>
-      <c r="AB3" s="158" t="n"/>
-      <c r="AC3" s="158" t="n"/>
     </row>
     <row r="4" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A4" s="148" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="B4" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C4" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D4" s="148" t="inlineStr">
-        <is>
-          <t>Pearl Jam</t>
-        </is>
-      </c>
-      <c r="E4" s="148" t="inlineStr">
+      <c r="A4" s="158" t="inlineStr">
+        <is>
+          <t>Angel From Montgomery</t>
+        </is>
+      </c>
+      <c r="B4" s="159" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C4" s="159" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D4" s="158" t="inlineStr">
+        <is>
+          <t>John Prine</t>
+        </is>
+      </c>
+      <c r="E4" s="158" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F4" s="150" t="n">
-        <v>0.003958333333333334</v>
-      </c>
-      <c r="G4" s="148" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="H4" s="148" t="n"/>
-      <c r="I4" s="148" t="n"/>
-      <c r="J4" s="148" t="inlineStr">
-        <is>
-          <t>90s</t>
-        </is>
-      </c>
-      <c r="K4" s="148" t="n"/>
+      <c r="F4" s="160" t="n">
+        <v>0.002766203703703704</v>
+      </c>
+      <c r="G4" s="158" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H4" s="158" t="n"/>
+      <c r="I4" s="158" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J4" s="158" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K4" s="158" t="n"/>
       <c r="L4" s="161">
         <f>COUNTIF(M4:AV4,"✓")</f>
         <v/>
       </c>
-      <c r="M4" s="151" t="n"/>
-      <c r="N4" s="151" t="n"/>
-      <c r="O4" s="152" t="n"/>
-      <c r="P4" s="148" t="n"/>
-      <c r="Q4" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="148" t="n"/>
-      <c r="T4" s="148" t="n"/>
-      <c r="U4" s="148" t="n"/>
-      <c r="V4" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W4" s="148" t="n"/>
-      <c r="X4" s="148" t="n"/>
-      <c r="Y4" s="148" t="n"/>
-      <c r="Z4" s="148" t="n"/>
-      <c r="AA4" s="148" t="n"/>
-      <c r="AB4" s="148" t="n"/>
-      <c r="AC4" s="148" t="n"/>
+      <c r="M4" s="161" t="n"/>
+      <c r="N4" s="161" t="n"/>
+      <c r="O4" s="162" t="n"/>
+      <c r="P4" s="158" t="n"/>
+      <c r="Q4" s="158" t="n"/>
+      <c r="R4" s="158" t="n"/>
+      <c r="S4" s="158" t="n"/>
+      <c r="T4" s="158" t="n"/>
+      <c r="U4" s="158" t="n"/>
+      <c r="V4" s="158" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W4" s="158" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X4" s="158" t="n"/>
+      <c r="Y4" s="158" t="n"/>
+      <c r="Z4" s="158" t="n"/>
+      <c r="AA4" s="158" t="n"/>
+      <c r="AB4" s="158" t="n"/>
+      <c r="AC4" s="158" t="n"/>
     </row>
     <row r="5" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A5" s="142" t="inlineStr">
-        <is>
-          <t>Bohemian Like You</t>
-        </is>
-      </c>
-      <c r="B5" s="153" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C5" s="143" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D5" s="142" t="inlineStr">
-        <is>
-          <t>Dandy Warhols</t>
-        </is>
-      </c>
-      <c r="E5" s="142" t="inlineStr">
+      <c r="A5" s="148" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="B5" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C5" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D5" s="148" t="inlineStr">
+        <is>
+          <t>Pearl Jam</t>
+        </is>
+      </c>
+      <c r="E5" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F5" s="144" t="n">
-        <v>0.002581018518518519</v>
-      </c>
-      <c r="G5" s="142" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="H5" s="142" t="n"/>
-      <c r="I5" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J5" s="142" t="inlineStr">
-        <is>
-          <t>00s</t>
-        </is>
-      </c>
-      <c r="K5" s="142" t="n"/>
+      <c r="F5" s="150" t="n">
+        <v>0.003958333333333334</v>
+      </c>
+      <c r="G5" s="148" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="H5" s="148" t="n"/>
+      <c r="I5" s="148" t="n"/>
+      <c r="J5" s="148" t="inlineStr">
+        <is>
+          <t>90s</t>
+        </is>
+      </c>
+      <c r="K5" s="148" t="n"/>
       <c r="L5" s="161">
         <f>COUNTIF(M5:AV5,"✓")</f>
         <v/>
       </c>
-      <c r="M5" s="145" t="n"/>
-      <c r="N5" s="145" t="n"/>
-      <c r="O5" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P5" s="142" t="n"/>
-      <c r="Q5" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="142" t="n"/>
-      <c r="T5" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="142" t="n"/>
-      <c r="V5" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W5" s="142" t="n"/>
-      <c r="X5" s="142" t="n"/>
-      <c r="Y5" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z5" s="142" t="n"/>
-      <c r="AA5" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB5" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC5" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M5" s="151" t="n"/>
+      <c r="N5" s="151" t="n"/>
+      <c r="O5" s="152" t="n"/>
+      <c r="P5" s="148" t="n"/>
+      <c r="Q5" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="148" t="n"/>
+      <c r="T5" s="148" t="n"/>
+      <c r="U5" s="148" t="n"/>
+      <c r="V5" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W5" s="148" t="n"/>
+      <c r="X5" s="148" t="n"/>
+      <c r="Y5" s="148" t="n"/>
+      <c r="Z5" s="148" t="n"/>
+      <c r="AA5" s="148" t="n"/>
+      <c r="AB5" s="148" t="n"/>
+      <c r="AC5" s="148" t="n"/>
     </row>
     <row r="6" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A6" s="148" t="inlineStr">
-        <is>
-          <t>Come Together</t>
-        </is>
-      </c>
-      <c r="B6" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C6" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D6" s="148" t="inlineStr">
-        <is>
-          <t>The Beatles</t>
-        </is>
-      </c>
-      <c r="E6" s="148" t="inlineStr">
+      <c r="A6" s="142" t="inlineStr">
+        <is>
+          <t>Bohemian Like You</t>
+        </is>
+      </c>
+      <c r="B6" s="153" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C6" s="143" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D6" s="142" t="inlineStr">
+        <is>
+          <t>Dandy Warhols</t>
+        </is>
+      </c>
+      <c r="E6" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F6" s="150" t="n">
-        <v>0.002719907407407407</v>
-      </c>
-      <c r="G6" s="148" t="inlineStr">
+      <c r="F6" s="144" t="n">
+        <v>0.002581018518518519</v>
+      </c>
+      <c r="G6" s="142" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="H6" s="148" t="n"/>
-      <c r="I6" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J6" s="148" t="inlineStr">
-        <is>
-          <t>60s</t>
-        </is>
-      </c>
-      <c r="K6" s="148" t="n"/>
+      <c r="H6" s="142" t="n"/>
+      <c r="I6" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J6" s="142" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="K6" s="142" t="n"/>
       <c r="L6" s="161">
         <f>COUNTIF(M6:AV6,"✓")</f>
         <v/>
       </c>
-      <c r="M6" s="151" t="n"/>
-      <c r="N6" s="151" t="n"/>
-      <c r="O6" s="152" t="n"/>
-      <c r="P6" s="148" t="n"/>
-      <c r="Q6" s="148" t="n"/>
-      <c r="R6" s="148" t="n"/>
-      <c r="S6" s="148" t="n"/>
-      <c r="T6" s="148" t="n"/>
-      <c r="U6" s="148" t="n"/>
-      <c r="V6" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W6" s="148" t="n"/>
-      <c r="X6" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y6" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z6" s="148" t="n"/>
-      <c r="AA6" s="148" t="n"/>
-      <c r="AB6" s="148" t="n"/>
-      <c r="AC6" s="148" t="inlineStr">
+      <c r="M6" s="145" t="n"/>
+      <c r="N6" s="145" t="n"/>
+      <c r="O6" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P6" s="142" t="n"/>
+      <c r="Q6" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="142" t="n"/>
+      <c r="T6" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="142" t="n"/>
+      <c r="V6" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W6" s="142" t="n"/>
+      <c r="X6" s="142" t="n"/>
+      <c r="Y6" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z6" s="142" t="n"/>
+      <c r="AA6" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB6" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC6" s="142" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A7" s="142" t="inlineStr">
-        <is>
-          <t>Crossroads</t>
-        </is>
-      </c>
-      <c r="B7" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C7" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D7" s="142" t="inlineStr">
-        <is>
-          <t>Cream</t>
-        </is>
-      </c>
-      <c r="E7" s="142" t="inlineStr">
+      <c r="A7" s="148" t="inlineStr">
+        <is>
+          <t>Come Together</t>
+        </is>
+      </c>
+      <c r="B7" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C7" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D7" s="148" t="inlineStr">
+        <is>
+          <t>The Beatles</t>
+        </is>
+      </c>
+      <c r="E7" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F7" s="144" t="n">
-        <v>0.003414351851851852</v>
-      </c>
-      <c r="G7" s="142" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H7" s="142" t="n"/>
-      <c r="I7" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J7" s="142" t="inlineStr">
+      <c r="F7" s="150" t="n">
+        <v>0.002719907407407407</v>
+      </c>
+      <c r="G7" s="148" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="H7" s="148" t="n"/>
+      <c r="I7" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J7" s="148" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="K7" s="142" t="n"/>
+      <c r="K7" s="148" t="n"/>
       <c r="L7" s="161">
         <f>COUNTIF(M7:AV7,"✓")</f>
         <v/>
       </c>
-      <c r="M7" s="145" t="n"/>
-      <c r="N7" s="145" t="n"/>
-      <c r="O7" s="142" t="n"/>
-      <c r="P7" s="142" t="n"/>
-      <c r="Q7" s="142" t="n"/>
-      <c r="R7" s="142" t="n"/>
-      <c r="S7" s="142" t="n"/>
-      <c r="T7" s="142" t="n"/>
-      <c r="U7" s="142" t="n"/>
-      <c r="V7" s="142" t="n"/>
-      <c r="W7" s="142" t="n"/>
-      <c r="X7" s="142" t="n"/>
-      <c r="Y7" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z7" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA7" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB7" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC7" s="142" t="inlineStr">
+      <c r="M7" s="151" t="n"/>
+      <c r="N7" s="151" t="n"/>
+      <c r="O7" s="152" t="n"/>
+      <c r="P7" s="148" t="n"/>
+      <c r="Q7" s="148" t="n"/>
+      <c r="R7" s="148" t="n"/>
+      <c r="S7" s="148" t="n"/>
+      <c r="T7" s="148" t="n"/>
+      <c r="U7" s="148" t="n"/>
+      <c r="V7" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W7" s="148" t="n"/>
+      <c r="X7" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y7" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z7" s="148" t="n"/>
+      <c r="AA7" s="148" t="n"/>
+      <c r="AB7" s="148" t="n"/>
+      <c r="AC7" s="148" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A8" s="148" t="inlineStr">
-        <is>
-          <t>Dedicated Follower Of Fashion</t>
-        </is>
-      </c>
-      <c r="B8" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C8" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D8" s="148" t="inlineStr">
-        <is>
-          <t>The King</t>
-        </is>
-      </c>
-      <c r="E8" s="148" t="inlineStr">
+      <c r="A8" s="142" t="inlineStr">
+        <is>
+          <t>Crossroads</t>
+        </is>
+      </c>
+      <c r="B8" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C8" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D8" s="142" t="inlineStr">
+        <is>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="E8" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F8" s="150" t="n">
-        <v>0.001747685185185185</v>
-      </c>
-      <c r="G8" s="148" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="H8" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I8" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J8" s="148" t="inlineStr">
+      <c r="F8" s="144" t="n">
+        <v>0.003414351851851852</v>
+      </c>
+      <c r="G8" s="142" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H8" s="142" t="n"/>
+      <c r="I8" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J8" s="142" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="K8" s="148" t="n"/>
+      <c r="K8" s="142" t="n"/>
       <c r="L8" s="161">
         <f>COUNTIF(M8:AV8,"✓")</f>
         <v/>
       </c>
-      <c r="M8" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N8" s="151" t="n"/>
-      <c r="O8" s="152" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P8" s="148" t="n"/>
-      <c r="Q8" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T8" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W8" s="148" t="n"/>
-      <c r="X8" s="148" t="n"/>
-      <c r="Y8" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z8" s="148" t="n"/>
-      <c r="AA8" s="148" t="n"/>
-      <c r="AB8" s="148" t="n"/>
-      <c r="AC8" s="148" t="n"/>
+      <c r="M8" s="145" t="n"/>
+      <c r="N8" s="145" t="n"/>
+      <c r="O8" s="142" t="n"/>
+      <c r="P8" s="142" t="n"/>
+      <c r="Q8" s="142" t="n"/>
+      <c r="R8" s="142" t="n"/>
+      <c r="S8" s="142" t="n"/>
+      <c r="T8" s="142" t="n"/>
+      <c r="U8" s="142" t="n"/>
+      <c r="V8" s="142" t="n"/>
+      <c r="W8" s="142" t="n"/>
+      <c r="X8" s="142" t="n"/>
+      <c r="Y8" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z8" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA8" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB8" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC8" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A9" s="142" t="inlineStr">
-        <is>
-          <t>Don't Let Me Down</t>
-        </is>
-      </c>
-      <c r="B9" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C9" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D9" s="142" t="inlineStr">
-        <is>
-          <t>The Beatles</t>
-        </is>
-      </c>
-      <c r="E9" s="142" t="inlineStr">
+      <c r="A9" s="148" t="inlineStr">
+        <is>
+          <t>Dedicated Follower Of Fashion</t>
+        </is>
+      </c>
+      <c r="B9" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C9" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D9" s="148" t="inlineStr">
+        <is>
+          <t>The King</t>
+        </is>
+      </c>
+      <c r="E9" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F9" s="144" t="n">
-        <v>0.0021875</v>
-      </c>
-      <c r="G9" s="142" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H9" s="142" t="n"/>
-      <c r="I9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J9" s="142" t="inlineStr">
+      <c r="F9" s="150" t="n">
+        <v>0.001747685185185185</v>
+      </c>
+      <c r="G9" s="148" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="H9" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I9" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J9" s="148" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="K9" s="142" t="n"/>
+      <c r="K9" s="148" t="n"/>
       <c r="L9" s="161">
         <f>COUNTIF(M9:AV9,"✓")</f>
         <v/>
       </c>
-      <c r="M9" s="145" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N9" s="145" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC9" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M9" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N9" s="151" t="n"/>
+      <c r="O9" s="152" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P9" s="148" t="n"/>
+      <c r="Q9" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T9" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W9" s="148" t="n"/>
+      <c r="X9" s="148" t="n"/>
+      <c r="Y9" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z9" s="148" t="n"/>
+      <c r="AA9" s="148" t="n"/>
+      <c r="AB9" s="148" t="n"/>
+      <c r="AC9" s="148" t="n"/>
     </row>
     <row r="10" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A10" s="148" t="inlineStr">
-        <is>
-          <t>Don't Look Back In Anger</t>
-        </is>
-      </c>
-      <c r="B10" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C10" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D10" s="148" t="inlineStr">
-        <is>
-          <t>Oasis</t>
-        </is>
-      </c>
-      <c r="E10" s="148" t="inlineStr">
+      <c r="A10" s="142" t="inlineStr">
+        <is>
+          <t>Don't Let Me Down</t>
+        </is>
+      </c>
+      <c r="B10" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C10" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D10" s="142" t="inlineStr">
+        <is>
+          <t>The Beatles</t>
+        </is>
+      </c>
+      <c r="E10" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F10" s="150" t="n">
-        <v>0.003344907407407408</v>
-      </c>
-      <c r="G10" s="148" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="H10" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I10" s="148" t="n"/>
-      <c r="J10" s="148" t="inlineStr">
-        <is>
-          <t>90s</t>
-        </is>
-      </c>
-      <c r="K10" s="148" t="n"/>
+      <c r="F10" s="144" t="n">
+        <v>0.0021875</v>
+      </c>
+      <c r="G10" s="142" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H10" s="142" t="n"/>
+      <c r="I10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J10" s="142" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="K10" s="142" t="n"/>
       <c r="L10" s="161">
         <f>COUNTIF(M10:AV10,"✓")</f>
         <v/>
       </c>
-      <c r="M10" s="151" t="n"/>
-      <c r="N10" s="151" t="n"/>
-      <c r="O10" s="152" t="n"/>
-      <c r="P10" s="148" t="n"/>
-      <c r="Q10" s="148" t="n"/>
-      <c r="R10" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="148" t="n"/>
-      <c r="T10" s="148" t="n"/>
-      <c r="U10" s="148" t="n"/>
-      <c r="V10" s="148" t="n"/>
-      <c r="W10" s="148" t="n"/>
-      <c r="X10" s="148" t="n"/>
-      <c r="Y10" s="148" t="n"/>
-      <c r="Z10" s="148" t="n"/>
-      <c r="AA10" s="148" t="n"/>
-      <c r="AB10" s="148" t="n"/>
-      <c r="AC10" s="148" t="n"/>
+      <c r="M10" s="145" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N10" s="145" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC10" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A11" s="142" t="inlineStr">
-        <is>
-          <t>Down By The River</t>
-        </is>
-      </c>
-      <c r="B11" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C11" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D11" s="142" t="inlineStr">
-        <is>
-          <t>Neil Young</t>
-        </is>
-      </c>
-      <c r="E11" s="142" t="inlineStr">
+      <c r="A11" s="148" t="inlineStr">
+        <is>
+          <t>Don't Look Back In Anger</t>
+        </is>
+      </c>
+      <c r="B11" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C11" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D11" s="148" t="inlineStr">
+        <is>
+          <t>Oasis</t>
+        </is>
+      </c>
+      <c r="E11" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F11" s="144" t="n">
-        <v>0.005555555555555556</v>
-      </c>
-      <c r="G11" s="142" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H11" s="142" t="n"/>
-      <c r="I11" s="142" t="n"/>
-      <c r="J11" s="142" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K11" s="142" t="n"/>
+      <c r="F11" s="150" t="n">
+        <v>0.003344907407407408</v>
+      </c>
+      <c r="G11" s="148" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="H11" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I11" s="148" t="n"/>
+      <c r="J11" s="148" t="inlineStr">
+        <is>
+          <t>90s</t>
+        </is>
+      </c>
+      <c r="K11" s="148" t="n"/>
       <c r="L11" s="161">
         <f>COUNTIF(M11:AV11,"✓")</f>
         <v/>
       </c>
-      <c r="M11" s="145" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N11" s="145" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O11" s="146" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P11" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T11" s="142" t="n"/>
-      <c r="U11" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W11" s="142" t="n"/>
-      <c r="X11" s="142" t="n"/>
-      <c r="Y11" s="142" t="n"/>
-      <c r="Z11" s="142" t="n"/>
-      <c r="AA11" s="142" t="n"/>
-      <c r="AB11" s="142" t="n"/>
-      <c r="AC11" s="142" t="n"/>
+      <c r="M11" s="151" t="n"/>
+      <c r="N11" s="151" t="n"/>
+      <c r="O11" s="152" t="n"/>
+      <c r="P11" s="148" t="n"/>
+      <c r="Q11" s="148" t="n"/>
+      <c r="R11" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="148" t="n"/>
+      <c r="T11" s="148" t="n"/>
+      <c r="U11" s="148" t="n"/>
+      <c r="V11" s="148" t="n"/>
+      <c r="W11" s="148" t="n"/>
+      <c r="X11" s="148" t="n"/>
+      <c r="Y11" s="148" t="n"/>
+      <c r="Z11" s="148" t="n"/>
+      <c r="AA11" s="148" t="n"/>
+      <c r="AB11" s="148" t="n"/>
+      <c r="AC11" s="148" t="n"/>
     </row>
     <row r="12" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A12" s="148" t="inlineStr">
-        <is>
-          <t>End Of The World</t>
-        </is>
-      </c>
-      <c r="B12" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C12" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D12" s="148" t="inlineStr">
-        <is>
-          <t>R.E.M.</t>
-        </is>
-      </c>
-      <c r="E12" s="148" t="inlineStr">
+      <c r="A12" s="142" t="inlineStr">
+        <is>
+          <t>Down By The River</t>
+        </is>
+      </c>
+      <c r="B12" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C12" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D12" s="142" t="inlineStr">
+        <is>
+          <t>Neil Young</t>
+        </is>
+      </c>
+      <c r="E12" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F12" s="150" t="n">
-        <v>0.002743055555555555</v>
-      </c>
-      <c r="G12" s="148" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="H12" s="148" t="n"/>
-      <c r="I12" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J12" s="148" t="inlineStr">
-        <is>
-          <t>80s</t>
-        </is>
-      </c>
-      <c r="K12" s="148" t="n"/>
+      <c r="F12" s="144" t="n">
+        <v>0.005555555555555556</v>
+      </c>
+      <c r="G12" s="142" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H12" s="142" t="n"/>
+      <c r="I12" s="142" t="n"/>
+      <c r="J12" s="142" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K12" s="142" t="n"/>
       <c r="L12" s="161">
         <f>COUNTIF(M12:AV12,"✓")</f>
         <v/>
       </c>
-      <c r="M12" s="151" t="n"/>
-      <c r="N12" s="151" t="n"/>
-      <c r="O12" s="148" t="n"/>
-      <c r="P12" s="148" t="n"/>
-      <c r="Q12" s="148" t="n"/>
-      <c r="R12" s="148" t="n"/>
-      <c r="S12" s="148" t="n"/>
-      <c r="T12" s="148" t="n"/>
-      <c r="U12" s="148" t="n"/>
-      <c r="V12" s="148" t="n"/>
-      <c r="W12" s="148" t="n"/>
-      <c r="X12" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y12" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z12" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA12" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB12" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC12" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M12" s="145" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N12" s="145" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O12" s="146" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P12" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T12" s="142" t="n"/>
+      <c r="U12" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W12" s="142" t="n"/>
+      <c r="X12" s="142" t="n"/>
+      <c r="Y12" s="142" t="n"/>
+      <c r="Z12" s="142" t="n"/>
+      <c r="AA12" s="142" t="n"/>
+      <c r="AB12" s="142" t="n"/>
+      <c r="AC12" s="142" t="n"/>
     </row>
     <row r="13" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A13" s="142" t="inlineStr">
-        <is>
-          <t>Follow Your Arrow</t>
-        </is>
-      </c>
-      <c r="B13" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C13" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D13" s="142" t="inlineStr">
-        <is>
-          <t>Kasey Musgraves</t>
-        </is>
-      </c>
-      <c r="E13" s="142" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F13" s="144" t="n">
-        <v>0.002303240740740741</v>
-      </c>
-      <c r="G13" s="142" t="inlineStr">
+      <c r="A13" s="148" t="inlineStr">
+        <is>
+          <t>End Of The World</t>
+        </is>
+      </c>
+      <c r="B13" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C13" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D13" s="148" t="inlineStr">
+        <is>
+          <t>R.E.M.</t>
+        </is>
+      </c>
+      <c r="E13" s="148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F13" s="150" t="n">
+        <v>0.002743055555555555</v>
+      </c>
+      <c r="G13" s="148" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="H13" s="142" t="n"/>
-      <c r="I13" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J13" s="142" t="inlineStr">
-        <is>
-          <t>10s</t>
-        </is>
-      </c>
-      <c r="K13" s="142" t="n"/>
+      <c r="H13" s="148" t="n"/>
+      <c r="I13" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J13" s="148" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="K13" s="148" t="n"/>
       <c r="L13" s="161">
         <f>COUNTIF(M13:AV13,"✓")</f>
         <v/>
       </c>
-      <c r="M13" s="145" t="n"/>
-      <c r="N13" s="145" t="n"/>
-      <c r="O13" s="146" t="n"/>
-      <c r="P13" s="142" t="n"/>
-      <c r="Q13" s="142" t="n"/>
-      <c r="R13" s="142" t="n"/>
-      <c r="S13" s="142" t="n"/>
-      <c r="T13" s="142" t="n"/>
-      <c r="U13" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W13" s="142" t="n"/>
-      <c r="X13" s="142" t="n"/>
-      <c r="Y13" s="142" t="n"/>
-      <c r="Z13" s="142" t="n"/>
-      <c r="AA13" s="142" t="n"/>
-      <c r="AB13" s="142" t="n"/>
-      <c r="AC13" s="142" t="n"/>
+      <c r="M13" s="151" t="n"/>
+      <c r="N13" s="151" t="n"/>
+      <c r="O13" s="148" t="n"/>
+      <c r="P13" s="148" t="n"/>
+      <c r="Q13" s="148" t="n"/>
+      <c r="R13" s="148" t="n"/>
+      <c r="S13" s="148" t="n"/>
+      <c r="T13" s="148" t="n"/>
+      <c r="U13" s="148" t="n"/>
+      <c r="V13" s="148" t="n"/>
+      <c r="W13" s="148" t="n"/>
+      <c r="X13" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y13" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z13" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA13" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB13" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC13" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A14" s="148" t="inlineStr">
-        <is>
-          <t>For What It's Worth</t>
-        </is>
-      </c>
-      <c r="B14" s="155" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C14" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D14" s="148" t="inlineStr">
-        <is>
-          <t>Buffalo Springfield</t>
-        </is>
-      </c>
-      <c r="E14" s="148" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F14" s="150" t="n">
-        <v>0.001770833333333333</v>
-      </c>
-      <c r="G14" s="148" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H14" s="148" t="n"/>
-      <c r="I14" s="148" t="n"/>
-      <c r="J14" s="148" t="inlineStr">
-        <is>
-          <t>60s</t>
-        </is>
-      </c>
-      <c r="K14" s="148" t="n"/>
+      <c r="A14" s="142" t="inlineStr">
+        <is>
+          <t>Follow Your Arrow</t>
+        </is>
+      </c>
+      <c r="B14" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C14" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D14" s="142" t="inlineStr">
+        <is>
+          <t>Kasey Musgraves</t>
+        </is>
+      </c>
+      <c r="E14" s="142" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F14" s="144" t="n">
+        <v>0.002303240740740741</v>
+      </c>
+      <c r="G14" s="142" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="H14" s="142" t="n"/>
+      <c r="I14" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J14" s="142" t="inlineStr">
+        <is>
+          <t>10s</t>
+        </is>
+      </c>
+      <c r="K14" s="142" t="n"/>
       <c r="L14" s="161">
         <f>COUNTIF(M14:AV14,"✓")</f>
         <v/>
       </c>
-      <c r="M14" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N14" s="151" t="n"/>
-      <c r="O14" s="152" t="n"/>
-      <c r="P14" s="148" t="n"/>
-      <c r="Q14" s="148" t="n"/>
-      <c r="R14" s="148" t="n"/>
-      <c r="S14" s="148" t="n"/>
-      <c r="T14" s="148" t="n"/>
-      <c r="U14" s="148" t="n"/>
-      <c r="V14" s="148" t="n"/>
-      <c r="W14" s="148" t="n"/>
-      <c r="X14" s="148" t="n"/>
-      <c r="Y14" s="148" t="n"/>
-      <c r="Z14" s="148" t="n"/>
-      <c r="AA14" s="148" t="n"/>
-      <c r="AB14" s="148" t="n"/>
-      <c r="AC14" s="148" t="n"/>
+      <c r="M14" s="145" t="n"/>
+      <c r="N14" s="145" t="n"/>
+      <c r="O14" s="146" t="n"/>
+      <c r="P14" s="142" t="n"/>
+      <c r="Q14" s="142" t="n"/>
+      <c r="R14" s="142" t="n"/>
+      <c r="S14" s="142" t="n"/>
+      <c r="T14" s="142" t="n"/>
+      <c r="U14" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W14" s="142" t="n"/>
+      <c r="X14" s="142" t="n"/>
+      <c r="Y14" s="142" t="n"/>
+      <c r="Z14" s="142" t="n"/>
+      <c r="AA14" s="142" t="n"/>
+      <c r="AB14" s="142" t="n"/>
+      <c r="AC14" s="142" t="n"/>
     </row>
     <row r="15" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A15" s="142" t="inlineStr">
-        <is>
-          <t>Fortunate Son</t>
-        </is>
-      </c>
-      <c r="B15" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C15" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D15" s="142" t="inlineStr">
-        <is>
-          <t>Credence Clearwater Revival</t>
-        </is>
-      </c>
-      <c r="E15" s="142" t="inlineStr">
+      <c r="A15" s="148" t="inlineStr">
+        <is>
+          <t>For What It's Worth</t>
+        </is>
+      </c>
+      <c r="B15" s="155" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C15" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D15" s="148" t="inlineStr">
+        <is>
+          <t>Buffalo Springfield</t>
+        </is>
+      </c>
+      <c r="E15" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F15" s="144" t="n">
-        <v>0.002789351851851852</v>
-      </c>
-      <c r="G15" s="142" t="inlineStr">
+      <c r="F15" s="150" t="n">
+        <v>0.001770833333333333</v>
+      </c>
+      <c r="G15" s="148" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="H15" s="142" t="n"/>
-      <c r="I15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J15" s="142" t="inlineStr">
+      <c r="H15" s="148" t="n"/>
+      <c r="I15" s="148" t="n"/>
+      <c r="J15" s="148" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="K15" s="142" t="n"/>
+      <c r="K15" s="148" t="n"/>
       <c r="L15" s="161">
         <f>COUNTIF(M15:AV15,"✓")</f>
         <v/>
       </c>
-      <c r="M15" s="145" t="n"/>
-      <c r="N15" s="145" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="142" t="n"/>
-      <c r="T15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X15" s="142" t="n"/>
-      <c r="Y15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z15" s="142" t="n"/>
-      <c r="AA15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC15" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M15" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N15" s="151" t="n"/>
+      <c r="O15" s="152" t="n"/>
+      <c r="P15" s="148" t="n"/>
+      <c r="Q15" s="148" t="n"/>
+      <c r="R15" s="148" t="n"/>
+      <c r="S15" s="148" t="n"/>
+      <c r="T15" s="148" t="n"/>
+      <c r="U15" s="148" t="n"/>
+      <c r="V15" s="148" t="n"/>
+      <c r="W15" s="148" t="n"/>
+      <c r="X15" s="148" t="n"/>
+      <c r="Y15" s="148" t="n"/>
+      <c r="Z15" s="148" t="n"/>
+      <c r="AA15" s="148" t="n"/>
+      <c r="AB15" s="148" t="n"/>
+      <c r="AC15" s="148" t="n"/>
     </row>
     <row r="16" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A16" s="148" t="inlineStr">
-        <is>
-          <t>Found Out About You</t>
-        </is>
-      </c>
-      <c r="B16" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C16" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D16" s="148" t="inlineStr">
-        <is>
-          <t>Gin Blossom</t>
-        </is>
-      </c>
-      <c r="E16" s="148" t="inlineStr">
+      <c r="A16" s="142" t="inlineStr">
+        <is>
+          <t>Fortunate Son</t>
+        </is>
+      </c>
+      <c r="B16" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C16" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D16" s="142" t="inlineStr">
+        <is>
+          <t>Credence Clearwater Revival</t>
+        </is>
+      </c>
+      <c r="E16" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F16" s="150" t="n">
-        <v>0.002488425925925926</v>
-      </c>
-      <c r="G16" s="148" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="H16" s="148" t="n"/>
-      <c r="I16" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J16" s="148" t="inlineStr">
-        <is>
-          <t>90s</t>
-        </is>
-      </c>
-      <c r="K16" s="148" t="n"/>
+      <c r="F16" s="144" t="n">
+        <v>0.002789351851851852</v>
+      </c>
+      <c r="G16" s="142" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H16" s="142" t="n"/>
+      <c r="I16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J16" s="142" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="K16" s="142" t="n"/>
       <c r="L16" s="161">
         <f>COUNTIF(M16:AV16,"✓")</f>
         <v/>
       </c>
-      <c r="M16" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N16" s="151" t="n"/>
-      <c r="O16" s="152" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P16" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q16" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="148" t="n"/>
-      <c r="T16" s="148" t="n"/>
-      <c r="U16" s="148" t="n"/>
-      <c r="V16" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W16" s="148" t="n"/>
-      <c r="X16" s="148" t="n"/>
-      <c r="Y16" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z16" s="148" t="n"/>
-      <c r="AA16" s="148" t="n"/>
-      <c r="AB16" s="148" t="n"/>
-      <c r="AC16" s="148" t="inlineStr">
+      <c r="M16" s="145" t="n"/>
+      <c r="N16" s="145" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="142" t="n"/>
+      <c r="T16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X16" s="142" t="n"/>
+      <c r="Y16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z16" s="142" t="n"/>
+      <c r="AA16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB16" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC16" s="142" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A17" s="142" t="inlineStr">
-        <is>
-          <t>From The Start</t>
-        </is>
-      </c>
-      <c r="B17" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C17" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D17" s="142" t="inlineStr">
-        <is>
-          <t>Laufey</t>
-        </is>
-      </c>
-      <c r="E17" s="142" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F17" s="144" t="n">
-        <v>0.00193287037037037</v>
-      </c>
-      <c r="G17" s="142" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="H17" s="142" t="n"/>
-      <c r="I17" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J17" s="142" t="inlineStr">
-        <is>
-          <t>20s</t>
-        </is>
-      </c>
-      <c r="K17" s="142" t="n"/>
+      <c r="A17" s="148" t="inlineStr">
+        <is>
+          <t>Found Out About You</t>
+        </is>
+      </c>
+      <c r="B17" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C17" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D17" s="148" t="inlineStr">
+        <is>
+          <t>Gin Blossom</t>
+        </is>
+      </c>
+      <c r="E17" s="148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F17" s="150" t="n">
+        <v>0.002488425925925926</v>
+      </c>
+      <c r="G17" s="148" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="H17" s="148" t="n"/>
+      <c r="I17" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J17" s="148" t="inlineStr">
+        <is>
+          <t>90s</t>
+        </is>
+      </c>
+      <c r="K17" s="148" t="n"/>
       <c r="L17" s="161">
         <f>COUNTIF(M17:AV17,"✓")</f>
         <v/>
       </c>
-      <c r="M17" s="145" t="n"/>
-      <c r="N17" s="145" t="n"/>
-      <c r="O17" s="146" t="n"/>
-      <c r="P17" s="142" t="n"/>
-      <c r="Q17" s="142" t="n"/>
-      <c r="R17" s="142" t="n"/>
-      <c r="S17" s="142" t="n"/>
-      <c r="T17" s="142" t="n"/>
-      <c r="U17" s="142" t="n"/>
-      <c r="V17" s="142" t="n"/>
-      <c r="W17" s="142" t="n"/>
-      <c r="X17" s="142" t="n"/>
-      <c r="Y17" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z17" s="142" t="n"/>
-      <c r="AA17" s="142" t="n"/>
-      <c r="AB17" s="142" t="n"/>
-      <c r="AC17" s="142" t="n"/>
+      <c r="M17" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N17" s="151" t="n"/>
+      <c r="O17" s="152" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P17" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="148" t="n"/>
+      <c r="T17" s="148" t="n"/>
+      <c r="U17" s="148" t="n"/>
+      <c r="V17" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W17" s="148" t="n"/>
+      <c r="X17" s="148" t="n"/>
+      <c r="Y17" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z17" s="148" t="n"/>
+      <c r="AA17" s="148" t="n"/>
+      <c r="AB17" s="148" t="n"/>
+      <c r="AC17" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A18" s="148" t="inlineStr">
-        <is>
-          <t>Guess Again</t>
-        </is>
-      </c>
-      <c r="B18" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C18" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D18" s="148" t="inlineStr">
-        <is>
-          <t>Jeff Tweedy</t>
-        </is>
-      </c>
-      <c r="E18" s="148" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F18" s="150" t="n">
-        <v>0.002430555555555556</v>
-      </c>
-      <c r="G18" s="148" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H18" s="148" t="n"/>
-      <c r="I18" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J18" s="148" t="inlineStr">
+      <c r="A18" s="142" t="inlineStr">
+        <is>
+          <t>From The Start</t>
+        </is>
+      </c>
+      <c r="B18" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C18" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D18" s="142" t="inlineStr">
+        <is>
+          <t>Laufey</t>
+        </is>
+      </c>
+      <c r="E18" s="142" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F18" s="144" t="n">
+        <v>0.00193287037037037</v>
+      </c>
+      <c r="G18" s="142" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="H18" s="142" t="n"/>
+      <c r="I18" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J18" s="142" t="inlineStr">
         <is>
           <t>20s</t>
         </is>
       </c>
-      <c r="K18" s="148" t="n"/>
+      <c r="K18" s="142" t="n"/>
       <c r="L18" s="161">
         <f>COUNTIF(M18:AV18,"✓")</f>
         <v/>
       </c>
-      <c r="M18" s="151" t="n"/>
-      <c r="N18" s="151" t="n"/>
-      <c r="O18" s="148" t="n"/>
-      <c r="P18" s="148" t="n"/>
-      <c r="Q18" s="148" t="n"/>
-      <c r="R18" s="148" t="n"/>
-      <c r="S18" s="148" t="n"/>
-      <c r="T18" s="148" t="n"/>
-      <c r="U18" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W18" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X18" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y18" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z18" s="148" t="n"/>
-      <c r="AA18" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB18" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC18" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M18" s="145" t="n"/>
+      <c r="N18" s="145" t="n"/>
+      <c r="O18" s="146" t="n"/>
+      <c r="P18" s="142" t="n"/>
+      <c r="Q18" s="142" t="n"/>
+      <c r="R18" s="142" t="n"/>
+      <c r="S18" s="142" t="n"/>
+      <c r="T18" s="142" t="n"/>
+      <c r="U18" s="142" t="n"/>
+      <c r="V18" s="142" t="n"/>
+      <c r="W18" s="142" t="n"/>
+      <c r="X18" s="142" t="n"/>
+      <c r="Y18" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z18" s="142" t="n"/>
+      <c r="AA18" s="142" t="n"/>
+      <c r="AB18" s="142" t="n"/>
+      <c r="AC18" s="142" t="n"/>
     </row>
     <row r="19" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A19" s="142" t="inlineStr">
-        <is>
-          <t>Head Over Heels</t>
-        </is>
-      </c>
-      <c r="B19" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C19" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D19" s="142" t="inlineStr">
-        <is>
-          <t>Tears for Fears</t>
-        </is>
-      </c>
-      <c r="E19" s="142" t="inlineStr">
+      <c r="A19" s="148" t="inlineStr">
+        <is>
+          <t>Guess Again</t>
+        </is>
+      </c>
+      <c r="B19" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C19" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D19" s="148" t="inlineStr">
+        <is>
+          <t>Jeff Tweedy</t>
+        </is>
+      </c>
+      <c r="E19" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F19" s="144" t="n">
-        <v>0.002604166666666667</v>
-      </c>
-      <c r="G19" s="142" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="H19" s="142" t="n"/>
-      <c r="I19" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J19" s="142" t="inlineStr">
-        <is>
-          <t>80s</t>
-        </is>
-      </c>
-      <c r="K19" s="142" t="n"/>
+      <c r="F19" s="150" t="n">
+        <v>0.002430555555555556</v>
+      </c>
+      <c r="G19" s="148" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H19" s="148" t="n"/>
+      <c r="I19" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J19" s="148" t="inlineStr">
+        <is>
+          <t>20s</t>
+        </is>
+      </c>
+      <c r="K19" s="148" t="n"/>
       <c r="L19" s="161">
         <f>COUNTIF(M19:AV19,"✓")</f>
         <v/>
       </c>
-      <c r="M19" s="145" t="n"/>
-      <c r="N19" s="145" t="n"/>
-      <c r="O19" s="142" t="n"/>
-      <c r="P19" s="142" t="n"/>
-      <c r="Q19" s="142" t="n"/>
-      <c r="R19" s="142" t="n"/>
-      <c r="S19" s="142" t="n"/>
-      <c r="T19" s="142" t="n"/>
-      <c r="U19" s="142" t="n"/>
-      <c r="V19" s="142" t="n"/>
-      <c r="W19" s="142" t="n"/>
-      <c r="X19" s="142" t="n"/>
-      <c r="Y19" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z19" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA19" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB19" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC19" s="142" t="inlineStr">
+      <c r="M19" s="151" t="n"/>
+      <c r="N19" s="151" t="n"/>
+      <c r="O19" s="148" t="n"/>
+      <c r="P19" s="148" t="n"/>
+      <c r="Q19" s="148" t="n"/>
+      <c r="R19" s="148" t="n"/>
+      <c r="S19" s="148" t="n"/>
+      <c r="T19" s="148" t="n"/>
+      <c r="U19" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W19" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X19" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y19" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z19" s="148" t="n"/>
+      <c r="AA19" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB19" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC19" s="148" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A20" s="148" t="inlineStr">
-        <is>
-          <t>Heroes</t>
-        </is>
-      </c>
-      <c r="B20" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C20" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D20" s="148" t="inlineStr">
-        <is>
-          <t>David Bowie</t>
-        </is>
-      </c>
-      <c r="E20" s="148" t="inlineStr">
+      <c r="A20" s="142" t="inlineStr">
+        <is>
+          <t>Head Over Heels</t>
+        </is>
+      </c>
+      <c r="B20" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C20" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D20" s="142" t="inlineStr">
+        <is>
+          <t>Tears for Fears</t>
+        </is>
+      </c>
+      <c r="E20" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F20" s="150" t="n">
-        <v>0.0046875</v>
-      </c>
-      <c r="G20" s="148" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="H20" s="148" t="n"/>
-      <c r="I20" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J20" s="148" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K20" s="148" t="n"/>
+      <c r="F20" s="144" t="n">
+        <v>0.002604166666666667</v>
+      </c>
+      <c r="G20" s="142" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="H20" s="142" t="n"/>
+      <c r="I20" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J20" s="142" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="K20" s="142" t="n"/>
       <c r="L20" s="161">
         <f>COUNTIF(M20:AV20,"✓")</f>
         <v/>
       </c>
-      <c r="M20" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N20" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O20" s="152" t="n"/>
-      <c r="P20" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q20" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="148" t="n"/>
-      <c r="T20" s="148" t="n"/>
-      <c r="U20" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W20" s="148" t="n"/>
-      <c r="X20" s="148" t="n"/>
-      <c r="Y20" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z20" s="148" t="n"/>
-      <c r="AA20" s="148" t="n"/>
-      <c r="AB20" s="148" t="n"/>
-      <c r="AC20" s="148" t="inlineStr">
+      <c r="M20" s="145" t="n"/>
+      <c r="N20" s="145" t="n"/>
+      <c r="O20" s="142" t="n"/>
+      <c r="P20" s="142" t="n"/>
+      <c r="Q20" s="142" t="n"/>
+      <c r="R20" s="142" t="n"/>
+      <c r="S20" s="142" t="n"/>
+      <c r="T20" s="142" t="n"/>
+      <c r="U20" s="142" t="n"/>
+      <c r="V20" s="142" t="n"/>
+      <c r="W20" s="142" t="n"/>
+      <c r="X20" s="142" t="n"/>
+      <c r="Y20" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z20" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA20" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB20" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC20" s="142" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A21" s="142" t="inlineStr">
-        <is>
-          <t>I've Got A Feeling</t>
-        </is>
-      </c>
-      <c r="B21" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C21" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D21" s="142" t="inlineStr">
-        <is>
-          <t>The Beates</t>
-        </is>
-      </c>
-      <c r="E21" s="142" t="inlineStr">
+      <c r="A21" s="148" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="B21" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C21" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D21" s="148" t="inlineStr">
+        <is>
+          <t>David Bowie</t>
+        </is>
+      </c>
+      <c r="E21" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F21" s="144" t="n">
-        <v>0.002511574074074074</v>
-      </c>
-      <c r="G21" s="142" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H21" s="142" t="n"/>
-      <c r="I21" s="142" t="n"/>
-      <c r="J21" s="142" t="inlineStr">
-        <is>
-          <t>60s</t>
-        </is>
-      </c>
-      <c r="K21" s="142" t="n"/>
+      <c r="F21" s="150" t="n">
+        <v>0.0046875</v>
+      </c>
+      <c r="G21" s="148" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="H21" s="148" t="n"/>
+      <c r="I21" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J21" s="148" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K21" s="148" t="n"/>
       <c r="L21" s="161">
         <f>COUNTIF(M21:AV21,"✓")</f>
         <v/>
       </c>
-      <c r="M21" s="145" t="n"/>
-      <c r="N21" s="145" t="n"/>
-      <c r="O21" s="146" t="n"/>
-      <c r="P21" s="142" t="n"/>
-      <c r="Q21" s="142" t="n"/>
-      <c r="R21" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="142" t="n"/>
-      <c r="T21" s="142" t="n"/>
-      <c r="U21" s="142" t="n"/>
-      <c r="V21" s="142" t="n"/>
-      <c r="W21" s="142" t="n"/>
-      <c r="X21" s="142" t="n"/>
-      <c r="Y21" s="142" t="n"/>
-      <c r="Z21" s="142" t="n"/>
-      <c r="AA21" s="142" t="n"/>
-      <c r="AB21" s="142" t="n"/>
-      <c r="AC21" s="142" t="n"/>
+      <c r="M21" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N21" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O21" s="152" t="n"/>
+      <c r="P21" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q21" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="148" t="n"/>
+      <c r="T21" s="148" t="n"/>
+      <c r="U21" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W21" s="148" t="n"/>
+      <c r="X21" s="148" t="n"/>
+      <c r="Y21" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z21" s="148" t="n"/>
+      <c r="AA21" s="148" t="n"/>
+      <c r="AB21" s="148" t="n"/>
+      <c r="AC21" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A22" s="148" t="inlineStr">
-        <is>
-          <t>Just Like Heaven</t>
-        </is>
-      </c>
-      <c r="B22" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C22" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D22" s="148" t="inlineStr">
-        <is>
-          <t>The Cure</t>
-        </is>
-      </c>
-      <c r="E22" s="148" t="inlineStr">
+      <c r="A22" s="142" t="inlineStr">
+        <is>
+          <t>I've Got A Feeling</t>
+        </is>
+      </c>
+      <c r="B22" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C22" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D22" s="142" t="inlineStr">
+        <is>
+          <t>The Beates</t>
+        </is>
+      </c>
+      <c r="E22" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F22" s="150" t="n">
-        <v>0.002581018518518519</v>
-      </c>
-      <c r="G22" s="148" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="H22" s="148" t="n"/>
-      <c r="I22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J22" s="148" t="inlineStr">
-        <is>
-          <t>80s</t>
-        </is>
-      </c>
-      <c r="K22" s="148" t="n"/>
+      <c r="F22" s="144" t="n">
+        <v>0.002511574074074074</v>
+      </c>
+      <c r="G22" s="142" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H22" s="142" t="n"/>
+      <c r="I22" s="142" t="n"/>
+      <c r="J22" s="142" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="K22" s="142" t="n"/>
       <c r="L22" s="161">
         <f>COUNTIF(M22:AV22,"✓")</f>
         <v/>
       </c>
-      <c r="M22" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N22" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X22" s="148" t="n"/>
-      <c r="Y22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC22" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M22" s="145" t="n"/>
+      <c r="N22" s="145" t="n"/>
+      <c r="O22" s="146" t="n"/>
+      <c r="P22" s="142" t="n"/>
+      <c r="Q22" s="142" t="n"/>
+      <c r="R22" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="142" t="n"/>
+      <c r="T22" s="142" t="n"/>
+      <c r="U22" s="142" t="n"/>
+      <c r="V22" s="142" t="n"/>
+      <c r="W22" s="142" t="n"/>
+      <c r="X22" s="142" t="n"/>
+      <c r="Y22" s="142" t="n"/>
+      <c r="Z22" s="142" t="n"/>
+      <c r="AA22" s="142" t="n"/>
+      <c r="AB22" s="142" t="n"/>
+      <c r="AC22" s="142" t="n"/>
     </row>
     <row r="23" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A23" s="142" t="inlineStr">
-        <is>
-          <t>Just What I Needed</t>
-        </is>
-      </c>
-      <c r="B23" s="143" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C23" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D23" s="142" t="inlineStr">
-        <is>
-          <t>The Cars</t>
-        </is>
-      </c>
-      <c r="E23" s="142" t="inlineStr">
+      <c r="A23" s="148" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="B23" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C23" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D23" s="148" t="inlineStr">
+        <is>
+          <t>The Cure</t>
+        </is>
+      </c>
+      <c r="E23" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F23" s="144" t="n">
-        <v>0.002604166666666667</v>
-      </c>
-      <c r="G23" s="142" t="inlineStr">
+      <c r="F23" s="150" t="n">
+        <v>0.002581018518518519</v>
+      </c>
+      <c r="G23" s="148" t="inlineStr">
         <is>
           <t>Matt</t>
         </is>
       </c>
-      <c r="H23" s="142" t="n"/>
-      <c r="I23" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J23" s="142" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K23" s="142" t="n"/>
+      <c r="H23" s="148" t="n"/>
+      <c r="I23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J23" s="148" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="K23" s="148" t="n"/>
       <c r="L23" s="161">
         <f>COUNTIF(M23:AV23,"✓")</f>
         <v/>
       </c>
-      <c r="M23" s="145" t="n"/>
-      <c r="N23" s="145" t="n"/>
-      <c r="O23" s="146" t="n"/>
-      <c r="P23" s="142" t="n"/>
-      <c r="Q23" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T23" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W23" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X23" s="142" t="n"/>
-      <c r="Y23" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z23" s="142" t="n"/>
-      <c r="AA23" s="142" t="n"/>
-      <c r="AB23" s="142" t="n"/>
-      <c r="AC23" s="142" t="n"/>
+      <c r="M23" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N23" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X23" s="148" t="n"/>
+      <c r="Y23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC23" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A24" s="148" t="inlineStr">
-        <is>
-          <t>Kings Of Ewing</t>
-        </is>
-      </c>
-      <c r="B24" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C24" s="156" t="n"/>
-      <c r="D24" s="148" t="inlineStr">
-        <is>
-          <t>Kings of Ewing</t>
-        </is>
-      </c>
-      <c r="E24" s="148" t="inlineStr">
+      <c r="A24" s="142" t="inlineStr">
+        <is>
+          <t>Just What I Needed</t>
+        </is>
+      </c>
+      <c r="B24" s="143" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C24" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D24" s="142" t="inlineStr">
+        <is>
+          <t>The Cars</t>
+        </is>
+      </c>
+      <c r="E24" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F24" s="150" t="n">
-        <v>0.003854166666666667</v>
-      </c>
-      <c r="G24" s="148" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="H24" s="148" t="n"/>
-      <c r="I24" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J24" s="148" t="inlineStr">
-        <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="K24" s="148" t="n"/>
+      <c r="F24" s="144" t="n">
+        <v>0.002604166666666667</v>
+      </c>
+      <c r="G24" s="142" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="H24" s="142" t="n"/>
+      <c r="I24" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J24" s="142" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K24" s="142" t="n"/>
       <c r="L24" s="161">
         <f>COUNTIF(M24:AV24,"✓")</f>
         <v/>
       </c>
-      <c r="M24" s="151" t="n"/>
-      <c r="N24" s="151" t="n"/>
-      <c r="O24" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P24" s="148" t="n"/>
-      <c r="Q24" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T24" s="148" t="n"/>
-      <c r="U24" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W24" s="148" t="n"/>
-      <c r="X24" s="148" t="n"/>
-      <c r="Y24" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z24" s="148" t="n"/>
-      <c r="AA24" s="148" t="n"/>
-      <c r="AB24" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC24" s="148" t="n"/>
+      <c r="M24" s="145" t="n"/>
+      <c r="N24" s="145" t="n"/>
+      <c r="O24" s="146" t="n"/>
+      <c r="P24" s="142" t="n"/>
+      <c r="Q24" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T24" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X24" s="142" t="n"/>
+      <c r="Y24" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z24" s="142" t="n"/>
+      <c r="AA24" s="142" t="n"/>
+      <c r="AB24" s="142" t="n"/>
+      <c r="AC24" s="142" t="n"/>
     </row>
     <row r="25" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A25" s="142" t="inlineStr">
-        <is>
-          <t>Laid</t>
-        </is>
-      </c>
-      <c r="B25" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C25" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D25" s="142" t="inlineStr">
-        <is>
-          <t>James</t>
-        </is>
-      </c>
-      <c r="E25" s="142" t="inlineStr">
+      <c r="A25" s="148" t="inlineStr">
+        <is>
+          <t>Kings Of Ewing</t>
+        </is>
+      </c>
+      <c r="B25" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C25" s="156" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/james/laid-official-2685951</t>
+        </is>
+      </c>
+      <c r="D25" s="148" t="inlineStr">
+        <is>
+          <t>Kings of Ewing</t>
+        </is>
+      </c>
+      <c r="E25" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F25" s="144" t="n">
-        <v>0.001979166666666667</v>
-      </c>
-      <c r="G25" s="142" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="H25" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I25" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J25" s="142" t="inlineStr">
-        <is>
-          <t>90s</t>
-        </is>
-      </c>
-      <c r="K25" s="142" t="n"/>
+      <c r="F25" s="150" t="n">
+        <v>0.003854166666666667</v>
+      </c>
+      <c r="G25" s="148" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="H25" s="148" t="n"/>
+      <c r="I25" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J25" s="148" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="K25" s="148" t="n"/>
       <c r="L25" s="161">
         <f>COUNTIF(M25:AV25,"✓")</f>
         <v/>
       </c>
-      <c r="M25" s="145" t="n"/>
-      <c r="N25" s="145" t="n"/>
-      <c r="O25" s="146" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P25" s="146" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q25" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T25" s="142" t="n"/>
-      <c r="U25" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W25" s="142" t="n"/>
-      <c r="X25" s="142" t="n"/>
-      <c r="Y25" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z25" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA25" s="142" t="n"/>
-      <c r="AB25" s="142" t="n"/>
-      <c r="AC25" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M25" s="151" t="n"/>
+      <c r="N25" s="151" t="n"/>
+      <c r="O25" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P25" s="148" t="n"/>
+      <c r="Q25" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T25" s="148" t="n"/>
+      <c r="U25" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W25" s="148" t="n"/>
+      <c r="X25" s="148" t="n"/>
+      <c r="Y25" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z25" s="148" t="n"/>
+      <c r="AA25" s="148" t="n"/>
+      <c r="AB25" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC25" s="148" t="n"/>
     </row>
     <row r="26" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A26" s="148" t="inlineStr">
-        <is>
-          <t>Let Me Roll It</t>
-        </is>
-      </c>
-      <c r="B26" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C26" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D26" s="148" t="inlineStr">
-        <is>
-          <t>Wings</t>
-        </is>
-      </c>
-      <c r="E26" s="148" t="inlineStr">
+      <c r="A26" s="142" t="inlineStr">
+        <is>
+          <t>Laid</t>
+        </is>
+      </c>
+      <c r="B26" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C26" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D26" s="142" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="E26" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F26" s="150" t="n">
-        <v>0.002650462962962963</v>
-      </c>
-      <c r="G26" s="148" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H26" s="148" t="n"/>
-      <c r="I26" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J26" s="148" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K26" s="148" t="n"/>
+      <c r="F26" s="144" t="n">
+        <v>0.001979166666666667</v>
+      </c>
+      <c r="G26" s="142" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="H26" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I26" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J26" s="142" t="inlineStr">
+        <is>
+          <t>90s</t>
+        </is>
+      </c>
+      <c r="K26" s="142" t="n"/>
       <c r="L26" s="161">
         <f>COUNTIF(M26:AV26,"✓")</f>
         <v/>
       </c>
-      <c r="M26" s="151" t="n"/>
-      <c r="N26" s="151" t="n"/>
-      <c r="O26" s="152" t="n"/>
-      <c r="P26" s="152" t="n"/>
-      <c r="Q26" s="152" t="n"/>
-      <c r="R26" s="152" t="n"/>
-      <c r="S26" s="152" t="n"/>
-      <c r="T26" s="152" t="n"/>
-      <c r="U26" s="152" t="n"/>
-      <c r="V26" s="152" t="n"/>
-      <c r="W26" s="152" t="n"/>
-      <c r="X26" s="152" t="n"/>
-      <c r="Y26" s="152" t="n"/>
-      <c r="Z26" s="152" t="n"/>
-      <c r="AA26" s="152" t="n"/>
-      <c r="AB26" s="152" t="n"/>
-      <c r="AC26" s="152" t="inlineStr">
+      <c r="M26" s="145" t="n"/>
+      <c r="N26" s="145" t="n"/>
+      <c r="O26" s="146" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P26" s="146" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q26" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T26" s="142" t="n"/>
+      <c r="U26" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W26" s="142" t="n"/>
+      <c r="X26" s="142" t="n"/>
+      <c r="Y26" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z26" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA26" s="142" t="n"/>
+      <c r="AB26" s="142" t="n"/>
+      <c r="AC26" s="142" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A27" s="142" t="inlineStr">
-        <is>
-          <t>Little By Little</t>
-        </is>
-      </c>
-      <c r="B27" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C27" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D27" s="142" t="inlineStr">
-        <is>
-          <t>Oasis</t>
-        </is>
-      </c>
-      <c r="E27" s="142" t="inlineStr">
+      <c r="A27" s="148" t="inlineStr">
+        <is>
+          <t>Let Me Roll It</t>
+        </is>
+      </c>
+      <c r="B27" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C27" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D27" s="148" t="inlineStr">
+        <is>
+          <t>Wings</t>
+        </is>
+      </c>
+      <c r="E27" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F27" s="144" t="n">
-        <v>0.003043981481481481</v>
-      </c>
-      <c r="G27" s="142" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="H27" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I27" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J27" s="142" t="inlineStr">
-        <is>
-          <t>00s</t>
-        </is>
-      </c>
-      <c r="K27" s="142" t="n"/>
+      <c r="F27" s="150" t="n">
+        <v>0.002650462962962963</v>
+      </c>
+      <c r="G27" s="148" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H27" s="148" t="n"/>
+      <c r="I27" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J27" s="148" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K27" s="148" t="n"/>
       <c r="L27" s="161">
         <f>COUNTIF(M27:AV27,"✓")</f>
         <v/>
       </c>
-      <c r="M27" s="145" t="n"/>
-      <c r="N27" s="145" t="n"/>
-      <c r="O27" s="142" t="n"/>
-      <c r="P27" s="142" t="n"/>
-      <c r="Q27" s="142" t="n"/>
-      <c r="R27" s="142" t="n"/>
-      <c r="S27" s="142" t="n"/>
-      <c r="T27" s="142" t="n"/>
-      <c r="U27" s="142" t="n"/>
-      <c r="V27" s="142" t="n"/>
-      <c r="W27" s="142" t="n"/>
-      <c r="X27" s="142" t="n"/>
-      <c r="Y27" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z27" s="142" t="n"/>
-      <c r="AA27" s="142" t="n"/>
-      <c r="AB27" s="142" t="n"/>
-      <c r="AC27" s="142" t="inlineStr">
+      <c r="M27" s="151" t="n"/>
+      <c r="N27" s="151" t="n"/>
+      <c r="O27" s="152" t="n"/>
+      <c r="P27" s="152" t="n"/>
+      <c r="Q27" s="152" t="n"/>
+      <c r="R27" s="152" t="n"/>
+      <c r="S27" s="152" t="n"/>
+      <c r="T27" s="152" t="n"/>
+      <c r="U27" s="152" t="n"/>
+      <c r="V27" s="152" t="n"/>
+      <c r="W27" s="152" t="n"/>
+      <c r="X27" s="152" t="n"/>
+      <c r="Y27" s="152" t="n"/>
+      <c r="Z27" s="152" t="n"/>
+      <c r="AA27" s="152" t="n"/>
+      <c r="AB27" s="152" t="n"/>
+      <c r="AC27" s="152" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A28" s="148" t="inlineStr">
-        <is>
-          <t>Message In A Bottle</t>
-        </is>
-      </c>
-      <c r="B28" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C28" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D28" s="148" t="inlineStr">
-        <is>
-          <t>The Police</t>
-        </is>
-      </c>
-      <c r="E28" s="148" t="inlineStr">
+      <c r="A28" s="142" t="inlineStr">
+        <is>
+          <t>Little By Little</t>
+        </is>
+      </c>
+      <c r="B28" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C28" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D28" s="142" t="inlineStr">
+        <is>
+          <t>Oasis</t>
+        </is>
+      </c>
+      <c r="E28" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F28" s="150" t="n">
-        <v>0.002858796296296296</v>
-      </c>
-      <c r="G28" s="148" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="H28" s="148" t="n"/>
-      <c r="I28" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J28" s="148" t="inlineStr">
-        <is>
-          <t>80s</t>
-        </is>
-      </c>
-      <c r="K28" s="148" t="n"/>
+      <c r="F28" s="144" t="n">
+        <v>0.003043981481481481</v>
+      </c>
+      <c r="G28" s="142" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="H28" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I28" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J28" s="142" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="K28" s="142" t="n"/>
       <c r="L28" s="161">
         <f>COUNTIF(M28:AV28,"✓")</f>
         <v/>
       </c>
-      <c r="M28" s="151" t="n"/>
-      <c r="N28" s="151" t="n"/>
-      <c r="O28" s="148" t="n"/>
-      <c r="P28" s="148" t="n"/>
-      <c r="Q28" s="148" t="n"/>
-      <c r="R28" s="148" t="n"/>
-      <c r="S28" s="148" t="n"/>
-      <c r="T28" s="148" t="n"/>
-      <c r="U28" s="148" t="n"/>
-      <c r="V28" s="148" t="n"/>
-      <c r="W28" s="148" t="n"/>
-      <c r="X28" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y28" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z28" s="148" t="n"/>
-      <c r="AA28" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB28" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC28" s="148" t="inlineStr">
+      <c r="M28" s="145" t="n"/>
+      <c r="N28" s="145" t="n"/>
+      <c r="O28" s="142" t="n"/>
+      <c r="P28" s="142" t="n"/>
+      <c r="Q28" s="142" t="n"/>
+      <c r="R28" s="142" t="n"/>
+      <c r="S28" s="142" t="n"/>
+      <c r="T28" s="142" t="n"/>
+      <c r="U28" s="142" t="n"/>
+      <c r="V28" s="142" t="n"/>
+      <c r="W28" s="142" t="n"/>
+      <c r="X28" s="142" t="n"/>
+      <c r="Y28" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z28" s="142" t="n"/>
+      <c r="AA28" s="142" t="n"/>
+      <c r="AB28" s="142" t="n"/>
+      <c r="AC28" s="142" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A29" s="142" t="inlineStr">
-        <is>
-          <t>Midnight Rider</t>
-        </is>
-      </c>
-      <c r="B29" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C29" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D29" s="142" t="inlineStr">
-        <is>
-          <t>The Allman Brothers Band</t>
-        </is>
-      </c>
-      <c r="E29" s="142" t="inlineStr">
+      <c r="A29" s="148" t="inlineStr">
+        <is>
+          <t>Message In A Bottle</t>
+        </is>
+      </c>
+      <c r="B29" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C29" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D29" s="148" t="inlineStr">
+        <is>
+          <t>The Police</t>
+        </is>
+      </c>
+      <c r="E29" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F29" s="144" t="n">
-        <v>0.002048611111111111</v>
-      </c>
-      <c r="G29" s="142" t="inlineStr">
+      <c r="F29" s="150" t="n">
+        <v>0.002858796296296296</v>
+      </c>
+      <c r="G29" s="148" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="H29" s="142" t="n"/>
-      <c r="I29" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J29" s="142" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K29" s="142" t="n"/>
+      <c r="H29" s="148" t="n"/>
+      <c r="I29" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J29" s="148" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="K29" s="148" t="n"/>
       <c r="L29" s="161">
         <f>COUNTIF(M29:AV29,"✓")</f>
         <v/>
       </c>
-      <c r="M29" s="145" t="n"/>
-      <c r="N29" s="145" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O29" s="146" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P29" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q29" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T29" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W29" s="142" t="n"/>
-      <c r="X29" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y29" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z29" s="142" t="n"/>
-      <c r="AA29" s="142" t="n"/>
-      <c r="AB29" s="142" t="n"/>
-      <c r="AC29" s="142" t="inlineStr">
+      <c r="M29" s="151" t="n"/>
+      <c r="N29" s="151" t="n"/>
+      <c r="O29" s="148" t="n"/>
+      <c r="P29" s="148" t="n"/>
+      <c r="Q29" s="148" t="n"/>
+      <c r="R29" s="148" t="n"/>
+      <c r="S29" s="148" t="n"/>
+      <c r="T29" s="148" t="n"/>
+      <c r="U29" s="148" t="n"/>
+      <c r="V29" s="148" t="n"/>
+      <c r="W29" s="148" t="n"/>
+      <c r="X29" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y29" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z29" s="148" t="n"/>
+      <c r="AA29" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB29" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC29" s="148" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A30" s="148" t="inlineStr">
-        <is>
-          <t>No One To Depend On</t>
-        </is>
-      </c>
-      <c r="B30" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C30" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D30" s="148" t="inlineStr">
-        <is>
-          <t>Santana</t>
-        </is>
-      </c>
-      <c r="E30" s="148" t="inlineStr">
+      <c r="A30" s="142" t="inlineStr">
+        <is>
+          <t>Midnight Rider</t>
+        </is>
+      </c>
+      <c r="B30" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C30" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D30" s="142" t="inlineStr">
+        <is>
+          <t>The Allman Brothers Band</t>
+        </is>
+      </c>
+      <c r="E30" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F30" s="150" t="n">
-        <v>0.003599537037037037</v>
-      </c>
-      <c r="G30" s="148" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="H30" s="148" t="n"/>
-      <c r="I30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J30" s="148" t="inlineStr">
+      <c r="F30" s="144" t="n">
+        <v>0.002048611111111111</v>
+      </c>
+      <c r="G30" s="142" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="H30" s="142" t="n"/>
+      <c r="I30" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J30" s="142" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="K30" s="148" t="n"/>
+      <c r="K30" s="142" t="n"/>
       <c r="L30" s="161">
         <f>COUNTIF(M30:AV30,"✓")</f>
         <v/>
       </c>
-      <c r="M30" s="151" t="n"/>
-      <c r="N30" s="151" t="n"/>
-      <c r="O30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB30" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC30" s="148" t="inlineStr">
+      <c r="M30" s="145" t="n"/>
+      <c r="N30" s="145" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O30" s="146" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P30" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q30" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T30" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W30" s="142" t="n"/>
+      <c r="X30" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y30" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z30" s="142" t="n"/>
+      <c r="AA30" s="142" t="n"/>
+      <c r="AB30" s="142" t="n"/>
+      <c r="AC30" s="142" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A31" s="142" t="inlineStr">
-        <is>
-          <t>Octopus's Garden</t>
-        </is>
-      </c>
-      <c r="B31" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C31" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D31" s="142" t="inlineStr">
-        <is>
-          <t>The Beatles</t>
-        </is>
-      </c>
-      <c r="E31" s="142" t="inlineStr">
+      <c r="A31" s="148" t="inlineStr">
+        <is>
+          <t>No One To Depend On</t>
+        </is>
+      </c>
+      <c r="B31" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C31" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D31" s="148" t="inlineStr">
+        <is>
+          <t>Santana</t>
+        </is>
+      </c>
+      <c r="E31" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F31" s="144" t="n">
-        <v>0.001967592592592592</v>
-      </c>
-      <c r="G31" s="142" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="H31" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I31" s="142" t="n"/>
-      <c r="J31" s="142" t="inlineStr">
-        <is>
-          <t>60s</t>
-        </is>
-      </c>
-      <c r="K31" s="142" t="n"/>
+      <c r="F31" s="150" t="n">
+        <v>0.003599537037037037</v>
+      </c>
+      <c r="G31" s="148" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="H31" s="148" t="n"/>
+      <c r="I31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J31" s="148" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K31" s="148" t="n"/>
       <c r="L31" s="161">
         <f>COUNTIF(M31:AV31,"✓")</f>
         <v/>
       </c>
-      <c r="M31" s="145" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N31" s="145" t="n"/>
-      <c r="O31" s="146" t="n"/>
-      <c r="P31" s="142" t="n"/>
-      <c r="Q31" s="142" t="n"/>
-      <c r="R31" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="142" t="n"/>
-      <c r="T31" s="142" t="n"/>
-      <c r="U31" s="142" t="n"/>
-      <c r="V31" s="142" t="n"/>
-      <c r="W31" s="142" t="n"/>
-      <c r="X31" s="142" t="n"/>
-      <c r="Y31" s="142" t="n"/>
-      <c r="Z31" s="142" t="n"/>
-      <c r="AA31" s="142" t="n"/>
-      <c r="AB31" s="142" t="n"/>
-      <c r="AC31" s="142" t="n"/>
+      <c r="M31" s="151" t="n"/>
+      <c r="N31" s="151" t="n"/>
+      <c r="O31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC31" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A32" s="148" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="B32" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C32" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D32" s="148" t="inlineStr">
-        <is>
-          <t>CSNY</t>
-        </is>
-      </c>
-      <c r="E32" s="148" t="inlineStr">
+      <c r="A32" s="142" t="inlineStr">
+        <is>
+          <t>Octopus's Garden</t>
+        </is>
+      </c>
+      <c r="B32" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C32" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D32" s="142" t="inlineStr">
+        <is>
+          <t>The Beatles</t>
+        </is>
+      </c>
+      <c r="E32" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F32" s="150" t="n">
-        <v>0.003229166666666667</v>
-      </c>
-      <c r="G32" s="148" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H32" s="148" t="n"/>
-      <c r="I32" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J32" s="148" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K32" s="148" t="n"/>
+      <c r="F32" s="144" t="n">
+        <v>0.001967592592592592</v>
+      </c>
+      <c r="G32" s="142" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="H32" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I32" s="142" t="n"/>
+      <c r="J32" s="142" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="K32" s="142" t="n"/>
       <c r="L32" s="161">
         <f>COUNTIF(M32:AV32,"✓")</f>
         <v/>
       </c>
-      <c r="M32" s="151" t="n"/>
-      <c r="N32" s="151" t="n"/>
-      <c r="O32" s="152" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P32" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q32" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="148" t="n"/>
-      <c r="T32" s="148" t="n"/>
-      <c r="U32" s="148" t="n"/>
-      <c r="V32" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W32" s="148" t="n"/>
-      <c r="X32" s="148" t="n"/>
-      <c r="Y32" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z32" s="148" t="n"/>
-      <c r="AA32" s="148" t="n"/>
-      <c r="AB32" s="148" t="n"/>
-      <c r="AC32" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M32" s="145" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N32" s="145" t="n"/>
+      <c r="O32" s="146" t="n"/>
+      <c r="P32" s="142" t="n"/>
+      <c r="Q32" s="142" t="n"/>
+      <c r="R32" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="142" t="n"/>
+      <c r="T32" s="142" t="n"/>
+      <c r="U32" s="142" t="n"/>
+      <c r="V32" s="142" t="n"/>
+      <c r="W32" s="142" t="n"/>
+      <c r="X32" s="142" t="n"/>
+      <c r="Y32" s="142" t="n"/>
+      <c r="Z32" s="142" t="n"/>
+      <c r="AA32" s="142" t="n"/>
+      <c r="AB32" s="142" t="n"/>
+      <c r="AC32" s="142" t="n"/>
     </row>
     <row r="33" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A33" s="142" t="inlineStr">
-        <is>
-          <t>Pink Pony Club</t>
-        </is>
-      </c>
-      <c r="B33" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C33" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D33" s="142" t="inlineStr">
-        <is>
-          <t>Chappel Roan</t>
-        </is>
-      </c>
-      <c r="E33" s="142" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F33" s="144" t="n">
-        <v>0.002951388888888889</v>
-      </c>
-      <c r="G33" s="142" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="H33" s="142" t="n"/>
-      <c r="I33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J33" s="142" t="inlineStr">
-        <is>
-          <t>20s</t>
-        </is>
-      </c>
-      <c r="K33" s="142" t="n"/>
+      <c r="A33" s="148" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="B33" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C33" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D33" s="148" t="inlineStr">
+        <is>
+          <t>CSNY</t>
+        </is>
+      </c>
+      <c r="E33" s="148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F33" s="150" t="n">
+        <v>0.003229166666666667</v>
+      </c>
+      <c r="G33" s="148" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H33" s="148" t="n"/>
+      <c r="I33" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J33" s="148" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K33" s="148" t="n"/>
       <c r="L33" s="161">
         <f>COUNTIF(M33:AV33,"✓")</f>
         <v/>
       </c>
-      <c r="M33" s="145" t="n"/>
-      <c r="N33" s="145" t="n"/>
-      <c r="O33" s="142" t="n"/>
-      <c r="P33" s="142" t="n"/>
-      <c r="Q33" s="142" t="n"/>
-      <c r="R33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB33" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC33" s="142" t="inlineStr">
+      <c r="M33" s="151" t="n"/>
+      <c r="N33" s="151" t="n"/>
+      <c r="O33" s="152" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P33" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="148" t="n"/>
+      <c r="T33" s="148" t="n"/>
+      <c r="U33" s="148" t="n"/>
+      <c r="V33" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W33" s="148" t="n"/>
+      <c r="X33" s="148" t="n"/>
+      <c r="Y33" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z33" s="148" t="n"/>
+      <c r="AA33" s="148" t="n"/>
+      <c r="AB33" s="148" t="n"/>
+      <c r="AC33" s="148" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A34" s="148" t="inlineStr">
-        <is>
-          <t>Riders On The Storm</t>
-        </is>
-      </c>
-      <c r="B34" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C34" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D34" s="148" t="inlineStr">
-        <is>
-          <t>The Door</t>
-        </is>
-      </c>
-      <c r="E34" s="148" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F34" s="150" t="n">
-        <v>0.004131944444444444</v>
-      </c>
-      <c r="G34" s="148" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H34" s="148" t="n"/>
-      <c r="I34" s="148" t="n"/>
-      <c r="J34" s="148" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K34" s="148" t="n"/>
+      <c r="A34" s="142" t="inlineStr">
+        <is>
+          <t>Pink Pony Club</t>
+        </is>
+      </c>
+      <c r="B34" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C34" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D34" s="142" t="inlineStr">
+        <is>
+          <t>Chappel Roan</t>
+        </is>
+      </c>
+      <c r="E34" s="142" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F34" s="144" t="n">
+        <v>0.002951388888888889</v>
+      </c>
+      <c r="G34" s="142" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="H34" s="142" t="n"/>
+      <c r="I34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J34" s="142" t="inlineStr">
+        <is>
+          <t>20s</t>
+        </is>
+      </c>
+      <c r="K34" s="142" t="n"/>
       <c r="L34" s="161">
         <f>COUNTIF(M34:AV34,"✓")</f>
         <v/>
       </c>
-      <c r="M34" s="151" t="n"/>
-      <c r="N34" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O34" s="152" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P34" s="148" t="n"/>
-      <c r="Q34" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="148" t="n"/>
-      <c r="T34" s="148" t="n"/>
-      <c r="U34" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W34" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X34" s="148" t="n"/>
-      <c r="Y34" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z34" s="148" t="n"/>
-      <c r="AA34" s="148" t="n"/>
-      <c r="AB34" s="148" t="n"/>
-      <c r="AC34" s="148" t="n"/>
+      <c r="M34" s="145" t="n"/>
+      <c r="N34" s="145" t="n"/>
+      <c r="O34" s="142" t="n"/>
+      <c r="P34" s="142" t="n"/>
+      <c r="Q34" s="142" t="n"/>
+      <c r="R34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC34" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A35" s="142" t="inlineStr">
-        <is>
-          <t>Rockin' In The Free World</t>
-        </is>
-      </c>
-      <c r="B35" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C35" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D35" s="142" t="inlineStr">
-        <is>
-          <t>Neil Young</t>
-        </is>
-      </c>
-      <c r="E35" s="142" t="inlineStr">
+      <c r="A35" s="148" t="inlineStr">
+        <is>
+          <t>Riders On The Storm</t>
+        </is>
+      </c>
+      <c r="B35" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C35" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D35" s="148" t="inlineStr">
+        <is>
+          <t>The Door</t>
+        </is>
+      </c>
+      <c r="E35" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F35" s="144" t="n">
-        <v>0.005960648148148148</v>
-      </c>
-      <c r="G35" s="142" t="inlineStr">
+      <c r="F35" s="150" t="n">
+        <v>0.004131944444444444</v>
+      </c>
+      <c r="G35" s="148" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="H35" s="142" t="n"/>
-      <c r="I35" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J35" s="142" t="inlineStr">
-        <is>
-          <t>80s</t>
-        </is>
-      </c>
-      <c r="K35" s="142" t="n"/>
+      <c r="H35" s="148" t="n"/>
+      <c r="I35" s="148" t="n"/>
+      <c r="J35" s="148" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K35" s="148" t="n"/>
       <c r="L35" s="161">
         <f>COUNTIF(M35:AV35,"✓")</f>
         <v/>
       </c>
-      <c r="M35" s="145" t="n"/>
-      <c r="N35" s="145" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O35" s="146" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P35" s="142" t="n"/>
-      <c r="Q35" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="142" t="n"/>
-      <c r="T35" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="142" t="n"/>
-      <c r="X35" s="142" t="n"/>
-      <c r="Y35" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z35" s="142" t="n"/>
-      <c r="AA35" s="142" t="n"/>
-      <c r="AB35" s="142" t="n"/>
-      <c r="AC35" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M35" s="151" t="n"/>
+      <c r="N35" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O35" s="152" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P35" s="148" t="n"/>
+      <c r="Q35" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="148" t="n"/>
+      <c r="T35" s="148" t="n"/>
+      <c r="U35" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X35" s="148" t="n"/>
+      <c r="Y35" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z35" s="148" t="n"/>
+      <c r="AA35" s="148" t="n"/>
+      <c r="AB35" s="148" t="n"/>
+      <c r="AC35" s="148" t="n"/>
     </row>
     <row r="36" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A36" s="148" t="inlineStr">
-        <is>
-          <t>Seven Nation Army</t>
-        </is>
-      </c>
-      <c r="B36" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C36" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D36" s="148" t="inlineStr">
-        <is>
-          <t>White Stripes</t>
-        </is>
-      </c>
-      <c r="E36" s="148" t="inlineStr">
+      <c r="A36" s="142" t="inlineStr">
+        <is>
+          <t>Rockin' In The Free World</t>
+        </is>
+      </c>
+      <c r="B36" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C36" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D36" s="142" t="inlineStr">
+        <is>
+          <t>Neil Young</t>
+        </is>
+      </c>
+      <c r="E36" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F36" s="150" t="n">
-        <v>0.002430555555555556</v>
-      </c>
-      <c r="G36" s="148" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="H36" s="148" t="n"/>
-      <c r="I36" s="148" t="n"/>
-      <c r="J36" s="148" t="inlineStr">
-        <is>
-          <t>00s</t>
-        </is>
-      </c>
-      <c r="K36" s="148" t="n"/>
+      <c r="F36" s="144" t="n">
+        <v>0.005960648148148148</v>
+      </c>
+      <c r="G36" s="142" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H36" s="142" t="n"/>
+      <c r="I36" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J36" s="142" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="K36" s="142" t="n"/>
       <c r="L36" s="161">
         <f>COUNTIF(M36:AV36,"✓")</f>
         <v/>
       </c>
-      <c r="M36" s="151" t="n"/>
-      <c r="N36" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O36" s="152" t="n"/>
-      <c r="P36" s="148" t="n"/>
-      <c r="Q36" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="148" t="n"/>
-      <c r="T36" s="148" t="n"/>
-      <c r="U36" s="148" t="n"/>
-      <c r="V36" s="148" t="n"/>
-      <c r="W36" s="148" t="n"/>
-      <c r="X36" s="148" t="n"/>
-      <c r="Y36" s="148" t="n"/>
-      <c r="Z36" s="148" t="n"/>
-      <c r="AA36" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB36" s="148" t="n"/>
-      <c r="AC36" s="148" t="n"/>
+      <c r="M36" s="145" t="n"/>
+      <c r="N36" s="145" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O36" s="146" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P36" s="142" t="n"/>
+      <c r="Q36" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="142" t="n"/>
+      <c r="T36" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W36" s="142" t="n"/>
+      <c r="X36" s="142" t="n"/>
+      <c r="Y36" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z36" s="142" t="n"/>
+      <c r="AA36" s="142" t="n"/>
+      <c r="AB36" s="142" t="n"/>
+      <c r="AC36" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A37" s="142" t="inlineStr">
-        <is>
-          <t>Smooth Operator</t>
-        </is>
-      </c>
-      <c r="B37" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C37" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D37" s="142" t="inlineStr">
-        <is>
-          <t>Sade</t>
-        </is>
-      </c>
-      <c r="E37" s="142" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F37" s="144" t="n">
-        <v>0.003368055555555556</v>
-      </c>
-      <c r="G37" s="142" t="inlineStr">
+      <c r="A37" s="148" t="inlineStr">
+        <is>
+          <t>Seven Nation Army</t>
+        </is>
+      </c>
+      <c r="B37" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C37" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D37" s="148" t="inlineStr">
+        <is>
+          <t>White Stripes</t>
+        </is>
+      </c>
+      <c r="E37" s="148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F37" s="150" t="n">
+        <v>0.002430555555555556</v>
+      </c>
+      <c r="G37" s="148" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="H37" s="142" t="n"/>
-      <c r="I37" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J37" s="142" t="inlineStr">
-        <is>
-          <t>80s</t>
-        </is>
-      </c>
-      <c r="K37" s="142" t="n"/>
+      <c r="H37" s="148" t="n"/>
+      <c r="I37" s="148" t="n"/>
+      <c r="J37" s="148" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="K37" s="148" t="n"/>
       <c r="L37" s="161">
         <f>COUNTIF(M37:AV37,"✓")</f>
         <v/>
       </c>
-      <c r="M37" s="145" t="n"/>
-      <c r="N37" s="145" t="n"/>
-      <c r="O37" s="142" t="n"/>
-      <c r="P37" s="142" t="n"/>
-      <c r="Q37" s="142" t="n"/>
-      <c r="R37" s="142" t="n"/>
-      <c r="S37" s="142" t="n"/>
-      <c r="T37" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W37" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X37" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y37" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z37" s="142" t="n"/>
-      <c r="AA37" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB37" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC37" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M37" s="151" t="n"/>
+      <c r="N37" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O37" s="152" t="n"/>
+      <c r="P37" s="148" t="n"/>
+      <c r="Q37" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="148" t="n"/>
+      <c r="T37" s="148" t="n"/>
+      <c r="U37" s="148" t="n"/>
+      <c r="V37" s="148" t="n"/>
+      <c r="W37" s="148" t="n"/>
+      <c r="X37" s="148" t="n"/>
+      <c r="Y37" s="148" t="n"/>
+      <c r="Z37" s="148" t="n"/>
+      <c r="AA37" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB37" s="148" t="n"/>
+      <c r="AC37" s="148" t="n"/>
     </row>
     <row r="38" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A38" s="148" t="inlineStr">
-        <is>
-          <t>Starlight</t>
-        </is>
-      </c>
-      <c r="B38" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C38" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D38" s="148" t="inlineStr">
-        <is>
-          <t>Muse</t>
-        </is>
-      </c>
-      <c r="E38" s="148" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F38" s="150" t="n">
-        <v>0.002604166666666667</v>
-      </c>
-      <c r="G38" s="148" t="inlineStr">
+      <c r="A38" s="142" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="B38" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C38" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D38" s="142" t="inlineStr">
+        <is>
+          <t>Sade</t>
+        </is>
+      </c>
+      <c r="E38" s="142" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F38" s="144" t="n">
+        <v>0.003368055555555556</v>
+      </c>
+      <c r="G38" s="142" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="H38" s="148" t="n"/>
-      <c r="I38" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J38" s="148" t="inlineStr">
-        <is>
-          <t>00s</t>
-        </is>
-      </c>
-      <c r="K38" s="148" t="n"/>
+      <c r="H38" s="142" t="n"/>
+      <c r="I38" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J38" s="142" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="K38" s="142" t="n"/>
       <c r="L38" s="161">
         <f>COUNTIF(M38:AV38,"✓")</f>
         <v/>
       </c>
-      <c r="M38" s="151" t="n"/>
-      <c r="N38" s="151" t="n"/>
-      <c r="O38" s="148" t="n"/>
-      <c r="P38" s="148" t="n"/>
-      <c r="Q38" s="148" t="n"/>
-      <c r="R38" s="148" t="n"/>
-      <c r="S38" s="148" t="n"/>
-      <c r="T38" s="148" t="n"/>
-      <c r="U38" s="148" t="n"/>
-      <c r="V38" s="148" t="n"/>
-      <c r="W38" s="148" t="n"/>
-      <c r="X38" s="148" t="n"/>
-      <c r="Y38" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z38" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA38" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB38" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC38" s="148" t="inlineStr">
+      <c r="M38" s="145" t="n"/>
+      <c r="N38" s="145" t="n"/>
+      <c r="O38" s="142" t="n"/>
+      <c r="P38" s="142" t="n"/>
+      <c r="Q38" s="142" t="n"/>
+      <c r="R38" s="142" t="n"/>
+      <c r="S38" s="142" t="n"/>
+      <c r="T38" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W38" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X38" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y38" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z38" s="142" t="n"/>
+      <c r="AA38" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB38" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC38" s="142" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A39" s="142" t="inlineStr">
-        <is>
-          <t>Sympathy For The Devil</t>
-        </is>
-      </c>
-      <c r="B39" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C39" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D39" s="142" t="inlineStr">
-        <is>
-          <t>Rolling Stones</t>
-        </is>
-      </c>
-      <c r="E39" s="142" t="inlineStr">
+      <c r="A39" s="148" t="inlineStr">
+        <is>
+          <t>Starlight</t>
+        </is>
+      </c>
+      <c r="B39" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C39" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D39" s="148" t="inlineStr">
+        <is>
+          <t>Muse</t>
+        </is>
+      </c>
+      <c r="E39" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F39" s="144" t="n">
-        <v>0.003472222222222222</v>
-      </c>
-      <c r="G39" s="142" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="H39" s="142" t="n"/>
-      <c r="I39" s="142" t="n"/>
-      <c r="J39" s="142" t="inlineStr">
-        <is>
-          <t>60s</t>
-        </is>
-      </c>
-      <c r="K39" s="142" t="n"/>
+      <c r="F39" s="150" t="n">
+        <v>0.002604166666666667</v>
+      </c>
+      <c r="G39" s="148" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="H39" s="148" t="n"/>
+      <c r="I39" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J39" s="148" t="inlineStr">
+        <is>
+          <t>00s</t>
+        </is>
+      </c>
+      <c r="K39" s="148" t="n"/>
       <c r="L39" s="161">
         <f>COUNTIF(M39:AV39,"✓")</f>
         <v/>
       </c>
-      <c r="M39" s="145" t="n"/>
-      <c r="N39" s="145" t="n"/>
-      <c r="O39" s="146" t="n"/>
-      <c r="P39" s="142" t="n"/>
-      <c r="Q39" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="142" t="n"/>
-      <c r="T39" s="142" t="n"/>
-      <c r="U39" s="142" t="n"/>
-      <c r="V39" s="142" t="n"/>
-      <c r="W39" s="142" t="n"/>
-      <c r="X39" s="142" t="n"/>
-      <c r="Y39" s="142" t="n"/>
-      <c r="Z39" s="142" t="n"/>
-      <c r="AA39" s="142" t="n"/>
-      <c r="AB39" s="142" t="n"/>
-      <c r="AC39" s="142" t="n"/>
+      <c r="M39" s="151" t="n"/>
+      <c r="N39" s="151" t="n"/>
+      <c r="O39" s="148" t="n"/>
+      <c r="P39" s="148" t="n"/>
+      <c r="Q39" s="148" t="n"/>
+      <c r="R39" s="148" t="n"/>
+      <c r="S39" s="148" t="n"/>
+      <c r="T39" s="148" t="n"/>
+      <c r="U39" s="148" t="n"/>
+      <c r="V39" s="148" t="n"/>
+      <c r="W39" s="148" t="n"/>
+      <c r="X39" s="148" t="n"/>
+      <c r="Y39" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z39" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA39" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB39" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC39" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A40" s="148" t="inlineStr">
-        <is>
-          <t>Teach Your Children</t>
-        </is>
-      </c>
-      <c r="B40" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C40" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D40" s="148" t="inlineStr">
-        <is>
-          <t>CSNY</t>
-        </is>
-      </c>
-      <c r="E40" s="148" t="inlineStr">
+      <c r="A40" s="142" t="inlineStr">
+        <is>
+          <t>Sympathy For The Devil</t>
+        </is>
+      </c>
+      <c r="B40" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C40" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D40" s="142" t="inlineStr">
+        <is>
+          <t>Rolling Stones</t>
+        </is>
+      </c>
+      <c r="E40" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F40" s="150" t="n">
-        <v>0.002002314814814815</v>
-      </c>
-      <c r="G40" s="148" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H40" s="148" t="n"/>
-      <c r="I40" s="148" t="n"/>
-      <c r="J40" s="148" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K40" s="148" t="n"/>
+      <c r="F40" s="144" t="n">
+        <v>0.003472222222222222</v>
+      </c>
+      <c r="G40" s="142" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="H40" s="142" t="n"/>
+      <c r="I40" s="142" t="n"/>
+      <c r="J40" s="142" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="K40" s="142" t="n"/>
       <c r="L40" s="161">
         <f>COUNTIF(M40:AV40,"✓")</f>
         <v/>
       </c>
-      <c r="M40" s="151" t="n"/>
-      <c r="N40" s="151" t="n"/>
-      <c r="O40" s="152" t="n"/>
-      <c r="P40" s="148" t="n"/>
-      <c r="Q40" s="148" t="n"/>
-      <c r="R40" s="148" t="n"/>
-      <c r="S40" s="148" t="n"/>
-      <c r="T40" s="148" t="n"/>
-      <c r="U40" s="148" t="n"/>
-      <c r="V40" s="148" t="n"/>
-      <c r="W40" s="148" t="n"/>
-      <c r="X40" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y40" s="148" t="n"/>
-      <c r="Z40" s="148" t="n"/>
-      <c r="AA40" s="148" t="n"/>
-      <c r="AB40" s="148" t="n"/>
-      <c r="AC40" s="148" t="n"/>
+      <c r="M40" s="145" t="n"/>
+      <c r="N40" s="145" t="n"/>
+      <c r="O40" s="146" t="n"/>
+      <c r="P40" s="142" t="n"/>
+      <c r="Q40" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="142" t="n"/>
+      <c r="T40" s="142" t="n"/>
+      <c r="U40" s="142" t="n"/>
+      <c r="V40" s="142" t="n"/>
+      <c r="W40" s="142" t="n"/>
+      <c r="X40" s="142" t="n"/>
+      <c r="Y40" s="142" t="n"/>
+      <c r="Z40" s="142" t="n"/>
+      <c r="AA40" s="142" t="n"/>
+      <c r="AB40" s="142" t="n"/>
+      <c r="AC40" s="142" t="n"/>
     </row>
     <row r="41" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A41" s="142" t="inlineStr">
-        <is>
-          <t>That's What I Love</t>
-        </is>
-      </c>
-      <c r="B41" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C41" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D41" s="142" t="inlineStr">
-        <is>
-          <t>Leon Bridges</t>
-        </is>
-      </c>
-      <c r="E41" s="142" t="inlineStr">
+      <c r="A41" s="148" t="inlineStr">
+        <is>
+          <t>Teach Your Children</t>
+        </is>
+      </c>
+      <c r="B41" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C41" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D41" s="148" t="inlineStr">
+        <is>
+          <t>CSNY</t>
+        </is>
+      </c>
+      <c r="E41" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F41" s="144" t="n">
-        <v>0.003460648148148148</v>
-      </c>
-      <c r="G41" s="142" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="H41" s="142" t="n"/>
-      <c r="I41" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J41" s="142" t="inlineStr">
-        <is>
-          <t>20s</t>
-        </is>
-      </c>
-      <c r="K41" s="142" t="n"/>
+      <c r="F41" s="150" t="n">
+        <v>0.002002314814814815</v>
+      </c>
+      <c r="G41" s="148" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H41" s="148" t="n"/>
+      <c r="I41" s="148" t="n"/>
+      <c r="J41" s="148" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K41" s="148" t="n"/>
       <c r="L41" s="161">
         <f>COUNTIF(M41:AV41,"✓")</f>
         <v/>
       </c>
-      <c r="M41" s="145" t="n"/>
-      <c r="N41" s="145" t="n"/>
-      <c r="O41" s="146" t="n"/>
-      <c r="P41" s="142" t="n"/>
-      <c r="Q41" s="142" t="n"/>
-      <c r="R41" s="142" t="n"/>
-      <c r="S41" s="142" t="n"/>
-      <c r="T41" s="142" t="n"/>
-      <c r="U41" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W41" s="142" t="n"/>
-      <c r="X41" s="142" t="n"/>
-      <c r="Y41" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z41" s="142" t="n"/>
-      <c r="AA41" s="142" t="n"/>
-      <c r="AB41" s="142" t="n"/>
-      <c r="AC41" s="142" t="n"/>
+      <c r="M41" s="151" t="n"/>
+      <c r="N41" s="151" t="n"/>
+      <c r="O41" s="152" t="n"/>
+      <c r="P41" s="148" t="n"/>
+      <c r="Q41" s="148" t="n"/>
+      <c r="R41" s="148" t="n"/>
+      <c r="S41" s="148" t="n"/>
+      <c r="T41" s="148" t="n"/>
+      <c r="U41" s="148" t="n"/>
+      <c r="V41" s="148" t="n"/>
+      <c r="W41" s="148" t="n"/>
+      <c r="X41" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y41" s="148" t="n"/>
+      <c r="Z41" s="148" t="n"/>
+      <c r="AA41" s="148" t="n"/>
+      <c r="AB41" s="148" t="n"/>
+      <c r="AC41" s="148" t="n"/>
     </row>
     <row r="42" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A42" s="148" t="inlineStr">
-        <is>
-          <t>The Seeker</t>
-        </is>
-      </c>
-      <c r="B42" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C42" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D42" s="148" t="inlineStr">
-        <is>
-          <t>The Who</t>
-        </is>
-      </c>
-      <c r="E42" s="148" t="inlineStr">
+      <c r="A42" s="142" t="inlineStr">
+        <is>
+          <t>That's What I Love</t>
+        </is>
+      </c>
+      <c r="B42" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C42" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D42" s="142" t="inlineStr">
+        <is>
+          <t>Leon Bridges</t>
+        </is>
+      </c>
+      <c r="E42" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F42" s="150" t="n">
-        <v>0.002256944444444444</v>
-      </c>
-      <c r="G42" s="148" t="inlineStr">
+      <c r="F42" s="144" t="n">
+        <v>0.003460648148148148</v>
+      </c>
+      <c r="G42" s="142" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="H42" s="148" t="n"/>
-      <c r="I42" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J42" s="148" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K42" s="148" t="n"/>
+      <c r="H42" s="142" t="n"/>
+      <c r="I42" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J42" s="142" t="inlineStr">
+        <is>
+          <t>20s</t>
+        </is>
+      </c>
+      <c r="K42" s="142" t="n"/>
       <c r="L42" s="161">
         <f>COUNTIF(M42:AV42,"✓")</f>
         <v/>
       </c>
-      <c r="M42" s="151" t="n"/>
-      <c r="N42" s="151" t="n"/>
-      <c r="O42" s="152" t="n"/>
-      <c r="P42" s="148" t="n"/>
-      <c r="Q42" s="148" t="n"/>
-      <c r="R42" s="148" t="n"/>
-      <c r="S42" s="148" t="n"/>
-      <c r="T42" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W42" s="148" t="n"/>
-      <c r="X42" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y42" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z42" s="148" t="n"/>
-      <c r="AA42" s="148" t="n"/>
-      <c r="AB42" s="148" t="n"/>
-      <c r="AC42" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M42" s="145" t="n"/>
+      <c r="N42" s="145" t="n"/>
+      <c r="O42" s="146" t="n"/>
+      <c r="P42" s="142" t="n"/>
+      <c r="Q42" s="142" t="n"/>
+      <c r="R42" s="142" t="n"/>
+      <c r="S42" s="142" t="n"/>
+      <c r="T42" s="142" t="n"/>
+      <c r="U42" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W42" s="142" t="n"/>
+      <c r="X42" s="142" t="n"/>
+      <c r="Y42" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z42" s="142" t="n"/>
+      <c r="AA42" s="142" t="n"/>
+      <c r="AB42" s="142" t="n"/>
+      <c r="AC42" s="142" t="n"/>
     </row>
     <row r="43" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A43" s="142" t="inlineStr">
-        <is>
-          <t>Voodoo Child</t>
-        </is>
-      </c>
-      <c r="B43" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C43" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D43" s="142" t="inlineStr">
-        <is>
-          <t>Jimi Hendrix</t>
-        </is>
-      </c>
-      <c r="E43" s="142" t="inlineStr">
+      <c r="A43" s="148" t="inlineStr">
+        <is>
+          <t>The Seeker</t>
+        </is>
+      </c>
+      <c r="B43" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C43" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D43" s="148" t="inlineStr">
+        <is>
+          <t>The Who</t>
+        </is>
+      </c>
+      <c r="E43" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F43" s="144" t="n">
-        <v>0.003472222222222222</v>
-      </c>
-      <c r="G43" s="142" t="inlineStr">
+      <c r="F43" s="150" t="n">
+        <v>0.002256944444444444</v>
+      </c>
+      <c r="G43" s="148" t="inlineStr">
         <is>
           <t>Drew</t>
         </is>
       </c>
-      <c r="H43" s="142" t="n"/>
-      <c r="I43" s="142" t="n"/>
-      <c r="J43" s="142" t="inlineStr">
-        <is>
-          <t>60s</t>
-        </is>
-      </c>
-      <c r="K43" s="142" t="n"/>
+      <c r="H43" s="148" t="n"/>
+      <c r="I43" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J43" s="148" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K43" s="148" t="n"/>
       <c r="L43" s="161">
         <f>COUNTIF(M43:AV43,"✓")</f>
         <v/>
       </c>
-      <c r="M43" s="145" t="n"/>
-      <c r="N43" s="145" t="n"/>
-      <c r="O43" s="146" t="n"/>
-      <c r="P43" s="142" t="n"/>
-      <c r="Q43" s="142" t="n"/>
-      <c r="R43" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="142" t="n"/>
-      <c r="T43" s="142" t="n"/>
-      <c r="U43" s="142" t="n"/>
-      <c r="V43" s="142" t="n"/>
-      <c r="W43" s="142" t="n"/>
-      <c r="X43" s="142" t="n"/>
-      <c r="Y43" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z43" s="142" t="n"/>
-      <c r="AA43" s="142" t="n"/>
-      <c r="AB43" s="142" t="n"/>
-      <c r="AC43" s="142" t="n"/>
+      <c r="M43" s="151" t="n"/>
+      <c r="N43" s="151" t="n"/>
+      <c r="O43" s="152" t="n"/>
+      <c r="P43" s="148" t="n"/>
+      <c r="Q43" s="148" t="n"/>
+      <c r="R43" s="148" t="n"/>
+      <c r="S43" s="148" t="n"/>
+      <c r="T43" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W43" s="148" t="n"/>
+      <c r="X43" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y43" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z43" s="148" t="n"/>
+      <c r="AA43" s="148" t="n"/>
+      <c r="AB43" s="148" t="n"/>
+      <c r="AC43" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A44" s="148" t="inlineStr">
-        <is>
-          <t>Walk On</t>
-        </is>
-      </c>
-      <c r="B44" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C44" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D44" s="148" t="inlineStr">
-        <is>
-          <t>Neil Young</t>
-        </is>
-      </c>
-      <c r="E44" s="148" t="inlineStr">
+      <c r="A44" s="142" t="inlineStr">
+        <is>
+          <t>Voodoo Child</t>
+        </is>
+      </c>
+      <c r="B44" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C44" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D44" s="142" t="inlineStr">
+        <is>
+          <t>Jimi Hendrix</t>
+        </is>
+      </c>
+      <c r="E44" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F44" s="150" t="n">
-        <v>0.002083333333333333</v>
-      </c>
-      <c r="G44" s="148" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H44" s="148" t="n"/>
-      <c r="I44" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J44" s="148" t="inlineStr">
-        <is>
-          <t>70s</t>
-        </is>
-      </c>
-      <c r="K44" s="148" t="n"/>
+      <c r="F44" s="144" t="n">
+        <v>0.003472222222222222</v>
+      </c>
+      <c r="G44" s="142" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="H44" s="142" t="n"/>
+      <c r="I44" s="142" t="n"/>
+      <c r="J44" s="142" t="inlineStr">
+        <is>
+          <t>60s</t>
+        </is>
+      </c>
+      <c r="K44" s="142" t="n"/>
       <c r="L44" s="161">
         <f>COUNTIF(M44:AV44,"✓")</f>
         <v/>
       </c>
-      <c r="M44" s="151" t="n"/>
-      <c r="N44" s="151" t="n"/>
-      <c r="O44" s="152" t="n"/>
-      <c r="P44" s="148" t="n"/>
-      <c r="Q44" s="148" t="n"/>
-      <c r="R44" s="148" t="n"/>
-      <c r="S44" s="148" t="n"/>
-      <c r="T44" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="148" t="n"/>
-      <c r="V44" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W44" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X44" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y44" s="148" t="n"/>
-      <c r="Z44" s="148" t="n"/>
-      <c r="AA44" s="148" t="n"/>
-      <c r="AB44" s="148" t="n"/>
-      <c r="AC44" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M44" s="145" t="n"/>
+      <c r="N44" s="145" t="n"/>
+      <c r="O44" s="146" t="n"/>
+      <c r="P44" s="142" t="n"/>
+      <c r="Q44" s="142" t="n"/>
+      <c r="R44" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="142" t="n"/>
+      <c r="T44" s="142" t="n"/>
+      <c r="U44" s="142" t="n"/>
+      <c r="V44" s="142" t="n"/>
+      <c r="W44" s="142" t="n"/>
+      <c r="X44" s="142" t="n"/>
+      <c r="Y44" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z44" s="142" t="n"/>
+      <c r="AA44" s="142" t="n"/>
+      <c r="AB44" s="142" t="n"/>
+      <c r="AC44" s="142" t="n"/>
     </row>
     <row r="45" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A45" s="142" t="inlineStr">
-        <is>
-          <t>War Pigs</t>
-        </is>
-      </c>
-      <c r="B45" s="154" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C45" s="154" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D45" s="142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Black Sabbath </t>
-        </is>
-      </c>
-      <c r="E45" s="142" t="inlineStr">
+      <c r="A45" s="148" t="inlineStr">
+        <is>
+          <t>Walk On</t>
+        </is>
+      </c>
+      <c r="B45" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C45" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D45" s="148" t="inlineStr">
+        <is>
+          <t>Neil Young</t>
+        </is>
+      </c>
+      <c r="E45" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F45" s="144" t="n">
-        <v>0.003125</v>
-      </c>
-      <c r="G45" s="142" t="inlineStr">
+      <c r="F45" s="150" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="G45" s="148" t="inlineStr">
         <is>
           <t>Miles</t>
         </is>
       </c>
-      <c r="H45" s="142" t="n"/>
-      <c r="I45" s="142" t="n"/>
-      <c r="J45" s="142" t="inlineStr">
+      <c r="H45" s="148" t="n"/>
+      <c r="I45" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J45" s="148" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="K45" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K45" s="148" t="n"/>
       <c r="L45" s="161">
         <f>COUNTIF(M45:AV45,"✓")</f>
         <v/>
       </c>
-      <c r="M45" s="145" t="n"/>
-      <c r="N45" s="145" t="n"/>
-      <c r="O45" s="146" t="n"/>
-      <c r="P45" s="142" t="n"/>
-      <c r="Q45" s="142" t="n"/>
-      <c r="R45" s="142" t="n"/>
-      <c r="S45" s="142" t="n"/>
-      <c r="T45" s="142" t="n"/>
-      <c r="U45" s="142" t="n"/>
-      <c r="V45" s="142" t="n"/>
-      <c r="W45" s="142" t="n"/>
-      <c r="X45" s="142" t="n"/>
-      <c r="Y45" s="142" t="n"/>
-      <c r="Z45" s="142" t="n"/>
-      <c r="AA45" s="142" t="n"/>
-      <c r="AB45" s="142" t="n"/>
-      <c r="AC45" s="142" t="n"/>
+      <c r="M45" s="151" t="n"/>
+      <c r="N45" s="151" t="n"/>
+      <c r="O45" s="152" t="n"/>
+      <c r="P45" s="148" t="n"/>
+      <c r="Q45" s="148" t="n"/>
+      <c r="R45" s="148" t="n"/>
+      <c r="S45" s="148" t="n"/>
+      <c r="T45" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="148" t="n"/>
+      <c r="V45" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W45" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X45" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y45" s="148" t="n"/>
+      <c r="Z45" s="148" t="n"/>
+      <c r="AA45" s="148" t="n"/>
+      <c r="AB45" s="148" t="n"/>
+      <c r="AC45" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="22" customFormat="1" customHeight="1" s="147">
-      <c r="A46" s="148" t="inlineStr">
-        <is>
-          <t>Whipping Post</t>
-        </is>
-      </c>
-      <c r="B46" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C46" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D46" s="148" t="inlineStr">
-        <is>
-          <t>The Allman Brothers Band</t>
-        </is>
-      </c>
-      <c r="E46" s="148" t="inlineStr">
+      <c r="A46" s="142" t="inlineStr">
+        <is>
+          <t>War Pigs</t>
+        </is>
+      </c>
+      <c r="B46" s="154" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C46" s="154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D46" s="142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Black Sabbath </t>
+        </is>
+      </c>
+      <c r="E46" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F46" s="150" t="n">
-        <v>0.003321759259259259</v>
-      </c>
-      <c r="G46" s="148" t="inlineStr">
-        <is>
-          <t>Drew</t>
-        </is>
-      </c>
-      <c r="H46" s="148" t="n"/>
-      <c r="I46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J46" s="148" t="inlineStr">
+      <c r="F46" s="144" t="n">
+        <v>0.003125</v>
+      </c>
+      <c r="G46" s="142" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H46" s="142" t="n"/>
+      <c r="I46" s="142" t="n"/>
+      <c r="J46" s="142" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="K46" s="148" t="n"/>
+      <c r="K46" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L46" s="161">
         <f>COUNTIF(M46:AV46,"✓")</f>
         <v/>
       </c>
-      <c r="M46" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N46" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC46" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M46" s="145" t="n"/>
+      <c r="N46" s="145" t="n"/>
+      <c r="O46" s="146" t="n"/>
+      <c r="P46" s="142" t="n"/>
+      <c r="Q46" s="142" t="n"/>
+      <c r="R46" s="142" t="n"/>
+      <c r="S46" s="142" t="n"/>
+      <c r="T46" s="142" t="n"/>
+      <c r="U46" s="142" t="n"/>
+      <c r="V46" s="142" t="n"/>
+      <c r="W46" s="142" t="n"/>
+      <c r="X46" s="142" t="n"/>
+      <c r="Y46" s="142" t="n"/>
+      <c r="Z46" s="142" t="n"/>
+      <c r="AA46" s="142" t="n"/>
+      <c r="AB46" s="142" t="n"/>
+      <c r="AC46" s="142" t="n"/>
     </row>
     <row r="47" ht="20" customFormat="1" customHeight="1" s="147">
-      <c r="A47" s="142" t="inlineStr">
-        <is>
-          <t>Who's That Lady</t>
-        </is>
-      </c>
-      <c r="B47" s="157" t="n"/>
-      <c r="C47" s="157" t="n"/>
-      <c r="D47" s="142" t="inlineStr">
-        <is>
-          <t>The Isley Brothers</t>
-        </is>
-      </c>
-      <c r="E47" s="142" t="inlineStr">
+      <c r="A47" s="148" t="inlineStr">
+        <is>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="B47" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C47" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D47" s="148" t="inlineStr">
+        <is>
+          <t>The Allman Brothers Band</t>
+        </is>
+      </c>
+      <c r="E47" s="148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F47" s="144" t="n"/>
-      <c r="G47" s="142" t="inlineStr">
-        <is>
-          <t>Instrumental</t>
-        </is>
-      </c>
-      <c r="H47" s="142" t="n"/>
-      <c r="I47" s="142" t="n"/>
-      <c r="J47" s="142" t="inlineStr">
+      <c r="F47" s="150" t="n">
+        <v>0.003321759259259259</v>
+      </c>
+      <c r="G47" s="148" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="H47" s="148" t="n"/>
+      <c r="I47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J47" s="148" t="inlineStr">
         <is>
           <t>70s</t>
         </is>
       </c>
-      <c r="K47" s="142" t="n"/>
+      <c r="K47" s="148" t="n"/>
       <c r="L47" s="161">
         <f>COUNTIF(M47:AV47,"✓")</f>
         <v/>
       </c>
-      <c r="M47" s="145" t="n"/>
-      <c r="N47" s="145" t="n"/>
-      <c r="O47" s="146" t="n"/>
-      <c r="P47" s="142" t="n"/>
-      <c r="Q47" s="142" t="n"/>
-      <c r="R47" s="142" t="n"/>
-      <c r="S47" s="142" t="n"/>
-      <c r="T47" s="142" t="n"/>
-      <c r="U47" s="142" t="n"/>
-      <c r="V47" s="142" t="n"/>
-      <c r="W47" s="142" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X47" s="142" t="n"/>
-      <c r="Y47" s="142" t="n"/>
-      <c r="Z47" s="142" t="n"/>
-      <c r="AA47" s="142" t="n"/>
-      <c r="AB47" s="142" t="n"/>
-      <c r="AC47" s="142" t="n"/>
+      <c r="M47" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N47" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC47" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="17" customFormat="1" customHeight="1" s="147">
-      <c r="A48" s="148" t="inlineStr">
-        <is>
-          <t>Won't Back Down</t>
-        </is>
-      </c>
-      <c r="B48" s="149" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C48" s="149" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D48" s="148" t="inlineStr">
-        <is>
-          <t>Tom Petty and the Heartbreakers</t>
-        </is>
-      </c>
-      <c r="E48" s="148" t="inlineStr">
+      <c r="A48" s="142" t="inlineStr">
+        <is>
+          <t>Who's That Lady</t>
+        </is>
+      </c>
+      <c r="B48" s="157" t="inlineStr">
+        <is>
+          <t>https://www.kingsofewing.com/docs/music/won%27t%20back%20down.pdf</t>
+        </is>
+      </c>
+      <c r="C48" s="157" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/tom-petty/i-wont-back-down-official-2175865</t>
+        </is>
+      </c>
+      <c r="D48" s="142" t="inlineStr">
+        <is>
+          <t>The Isley Brothers</t>
+        </is>
+      </c>
+      <c r="E48" s="142" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F48" s="150" t="n">
-        <v>0.002094907407407407</v>
-      </c>
-      <c r="G48" s="148" t="inlineStr">
-        <is>
-          <t>Miles</t>
-        </is>
-      </c>
-      <c r="H48" s="148" t="n"/>
-      <c r="I48" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J48" s="148" t="inlineStr">
-        <is>
-          <t>80s</t>
-        </is>
-      </c>
-      <c r="K48" s="148" t="n"/>
+      <c r="F48" s="144" t="n"/>
+      <c r="G48" s="142" t="inlineStr">
+        <is>
+          <t>Instrumental</t>
+        </is>
+      </c>
+      <c r="H48" s="142" t="n"/>
+      <c r="I48" s="142" t="n"/>
+      <c r="J48" s="142" t="inlineStr">
+        <is>
+          <t>70s</t>
+        </is>
+      </c>
+      <c r="K48" s="142" t="n"/>
       <c r="L48" s="161">
         <f>COUNTIF(M48:AV48,"✓")</f>
         <v/>
       </c>
-      <c r="M48" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N48" s="151" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O48" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P48" s="148" t="n"/>
-      <c r="Q48" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="148" t="n"/>
-      <c r="T48" s="148" t="n"/>
-      <c r="U48" s="148" t="n"/>
-      <c r="V48" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W48" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X48" s="148" t="n"/>
-      <c r="Y48" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z48" s="148" t="n"/>
-      <c r="AA48" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB48" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC48" s="148" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M48" s="145" t="n"/>
+      <c r="N48" s="145" t="n"/>
+      <c r="O48" s="146" t="n"/>
+      <c r="P48" s="142" t="n"/>
+      <c r="Q48" s="142" t="n"/>
+      <c r="R48" s="142" t="n"/>
+      <c r="S48" s="142" t="n"/>
+      <c r="T48" s="142" t="n"/>
+      <c r="U48" s="142" t="n"/>
+      <c r="V48" s="142" t="n"/>
+      <c r="W48" s="142" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X48" s="142" t="n"/>
+      <c r="Y48" s="142" t="n"/>
+      <c r="Z48" s="142" t="n"/>
+      <c r="AA48" s="142" t="n"/>
+      <c r="AB48" s="142" t="n"/>
+      <c r="AC48" s="142" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n"/>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="28" t="n"/>
-      <c r="E49" s="28" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
-      <c r="J49" s="7" t="n"/>
-      <c r="K49" s="7" t="n"/>
-      <c r="L49" s="7" t="n"/>
-      <c r="M49" s="7" t="n"/>
-      <c r="N49" s="7" t="n"/>
-      <c r="O49" s="7" t="n"/>
-      <c r="P49" s="7" t="n"/>
-      <c r="Q49" s="7" t="n"/>
-      <c r="R49" s="7" t="n"/>
-      <c r="S49" s="7" t="n"/>
-      <c r="T49" s="7" t="n"/>
-      <c r="U49" s="7" t="n"/>
-      <c r="V49" s="7" t="n"/>
-      <c r="W49" s="7" t="n"/>
-      <c r="X49" s="7" t="n"/>
-      <c r="Y49" s="7" t="n"/>
-      <c r="Z49" s="7" t="n"/>
-      <c r="AA49" s="7" t="n"/>
-      <c r="AB49" s="7" t="n"/>
-      <c r="AC49" s="7" t="n"/>
+      <c r="A49" s="148" t="inlineStr">
+        <is>
+          <t>Won't Back Down</t>
+        </is>
+      </c>
+      <c r="B49" s="149" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C49" s="149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D49" s="148" t="inlineStr">
+        <is>
+          <t>Tom Petty and the Heartbreakers</t>
+        </is>
+      </c>
+      <c r="E49" s="148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F49" s="150" t="n">
+        <v>0.002094907407407407</v>
+      </c>
+      <c r="G49" s="148" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
+      <c r="H49" s="148" t="n"/>
+      <c r="I49" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J49" s="148" t="inlineStr">
+        <is>
+          <t>80s</t>
+        </is>
+      </c>
+      <c r="K49" s="148" t="n"/>
+      <c r="L49" s="161">
+        <f>COUNTIF(M49:AV49,"✓")</f>
+        <v/>
+      </c>
+      <c r="M49" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N49" s="151" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O49" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P49" s="148" t="n"/>
+      <c r="Q49" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="148" t="n"/>
+      <c r="T49" s="148" t="n"/>
+      <c r="U49" s="148" t="n"/>
+      <c r="V49" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W49" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X49" s="148" t="n"/>
+      <c r="Y49" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z49" s="148" t="n"/>
+      <c r="AA49" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB49" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC49" s="148" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+      <c r="J50" s="7" t="n"/>
+      <c r="K50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
+      <c r="N50" s="7" t="n"/>
+      <c r="O50" s="7" t="n"/>
+      <c r="P50" s="7" t="n"/>
+      <c r="Q50" s="7" t="n"/>
+      <c r="R50" s="7" t="n"/>
+      <c r="S50" s="7" t="n"/>
+      <c r="T50" s="7" t="n"/>
+      <c r="U50" s="7" t="n"/>
+      <c r="V50" s="7" t="n"/>
+      <c r="W50" s="7" t="n"/>
+      <c r="X50" s="7" t="n"/>
+      <c r="Y50" s="7" t="n"/>
+      <c r="Z50" s="7" t="n"/>
+      <c r="AA50" s="7" t="n"/>
+      <c r="AB50" s="7" t="n"/>
+      <c r="AC50" s="7" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7064,7 +7127,7 @@
         </is>
       </c>
       <c r="F8" s="42">
-        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -7205,7 +7268,7 @@
         </is>
       </c>
       <c r="F13" s="42">
-        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -7555,7 +7618,7 @@
         </is>
       </c>
       <c r="F8" s="42">
-        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -7692,7 +7755,7 @@
         </is>
       </c>
       <c r="F13" s="42">
-        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -7749,7 +7812,7 @@
         </is>
       </c>
       <c r="F15" s="42">
-        <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -8038,7 +8101,7 @@
         </is>
       </c>
       <c r="F7" s="42">
-        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -8143,7 +8206,7 @@
         </is>
       </c>
       <c r="F11" s="42">
-        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -8200,7 +8263,7 @@
         </is>
       </c>
       <c r="F13" s="42">
-        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -8393,7 +8456,7 @@
         </is>
       </c>
       <c r="F20" s="42">
-        <f>VLOOKUP(B20,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B20,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -8558,7 +8621,7 @@
         </is>
       </c>
       <c r="F26" s="42">
-        <f>VLOOKUP(B26,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B26,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -8615,7 +8678,7 @@
         </is>
       </c>
       <c r="F28" s="42">
-        <f>VLOOKUP(B28,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B28,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -8971,7 +9034,7 @@
         </is>
       </c>
       <c r="F7" s="42">
-        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -9056,7 +9119,7 @@
         </is>
       </c>
       <c r="F10" s="42">
-        <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -9221,7 +9284,7 @@
         </is>
       </c>
       <c r="F16" s="42">
-        <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -9589,7 +9652,7 @@
         </is>
       </c>
       <c r="F4" s="42">
-        <f>VLOOKUP(B4,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B4,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -9782,7 +9845,7 @@
         </is>
       </c>
       <c r="F11" s="42">
-        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -10227,7 +10290,7 @@
         </is>
       </c>
       <c r="F8" s="42">
-        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -10332,7 +10395,7 @@
         </is>
       </c>
       <c r="F12" s="42">
-        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -10740,7 +10803,7 @@
         </is>
       </c>
       <c r="F11" s="42">
-        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -10769,7 +10832,7 @@
         </is>
       </c>
       <c r="F12" s="42">
-        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -10798,7 +10861,7 @@
         </is>
       </c>
       <c r="F13" s="42">
-        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -10907,7 +10970,7 @@
         </is>
       </c>
       <c r="F17" s="42">
-        <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -10932,7 +10995,7 @@
         </is>
       </c>
       <c r="F18" s="42">
-        <f>VLOOKUP(B18,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B18,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -10961,7 +11024,7 @@
         </is>
       </c>
       <c r="F19" s="42">
-        <f>VLOOKUP(B19,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B19,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -10990,7 +11053,7 @@
         </is>
       </c>
       <c r="F20" s="42">
-        <f>VLOOKUP(B20,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B20,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -11075,7 +11138,7 @@
         </is>
       </c>
       <c r="F23" s="42">
-        <f>VLOOKUP(B23,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B23,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -11244,7 +11307,7 @@
         </is>
       </c>
       <c r="F29" s="42">
-        <f>VLOOKUP(B29,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B29,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -11626,7 +11689,7 @@
         </is>
       </c>
       <c r="F11" s="42">
-        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -11655,7 +11718,7 @@
         </is>
       </c>
       <c r="F12" s="42">
-        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -11736,7 +11799,7 @@
         </is>
       </c>
       <c r="F15" s="42">
-        <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -11761,7 +11824,7 @@
         </is>
       </c>
       <c r="F16" s="42">
-        <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -11818,7 +11881,7 @@
         </is>
       </c>
       <c r="F18" s="42">
-        <f>VLOOKUP(B18,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B18,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -12386,7 +12449,7 @@
         </is>
       </c>
       <c r="F12" s="42">
-        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -12824,7 +12887,7 @@
         </is>
       </c>
       <c r="F12" s="42">
-        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -13556,7 +13619,7 @@
         </is>
       </c>
       <c r="F8" s="42">
-        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -13585,7 +13648,7 @@
         </is>
       </c>
       <c r="F9" s="42">
-        <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -13939,7 +14002,7 @@
         </is>
       </c>
       <c r="F6" s="42">
-        <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -13968,7 +14031,7 @@
         </is>
       </c>
       <c r="F7" s="42">
-        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -14049,7 +14112,7 @@
         </is>
       </c>
       <c r="F10" s="42">
-        <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15188,7 +15251,7 @@
         </is>
       </c>
       <c r="F4" s="99">
-        <f>VLOOKUP(B4,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B4,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15217,7 +15280,7 @@
         </is>
       </c>
       <c r="F5" s="112">
-        <f>VLOOKUP(B5,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B5,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15246,7 +15309,7 @@
         </is>
       </c>
       <c r="F6" s="101">
-        <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15275,7 +15338,7 @@
         </is>
       </c>
       <c r="F7" s="112">
-        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15304,7 +15367,7 @@
         </is>
       </c>
       <c r="F8" s="101">
-        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15333,7 +15396,7 @@
         </is>
       </c>
       <c r="F9" s="112">
-        <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15362,7 +15425,7 @@
         </is>
       </c>
       <c r="F10" s="101">
-        <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15391,7 +15454,7 @@
         </is>
       </c>
       <c r="F11" s="112">
-        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15420,7 +15483,7 @@
         </is>
       </c>
       <c r="F12" s="101">
-        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15449,7 +15512,7 @@
         </is>
       </c>
       <c r="F13" s="112">
-        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15478,7 +15541,7 @@
         </is>
       </c>
       <c r="F14" s="101">
-        <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15507,7 +15570,7 @@
         </is>
       </c>
       <c r="F15" s="112">
-        <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15536,7 +15599,7 @@
         </is>
       </c>
       <c r="F16" s="101">
-        <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15565,7 +15628,7 @@
         </is>
       </c>
       <c r="F17" s="112">
-        <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -15594,7 +15657,7 @@
         </is>
       </c>
       <c r="F18" s="104">
-        <f>VLOOKUP(B18,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B18,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -16832,7 +16895,7 @@
         </is>
       </c>
       <c r="F11" s="45">
-        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -17225,7 +17288,7 @@
         </is>
       </c>
       <c r="F4" s="42">
-        <f>VLOOKUP(B4,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B4,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -18976,7 +19039,7 @@
         </is>
       </c>
       <c r="F31" s="42">
-        <f>VLOOKUP(B31,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B31,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -19061,7 +19124,7 @@
         </is>
       </c>
       <c r="F34" s="42">
-        <f>VLOOKUP(B34,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <f>VLOOKUP(B34,'Song Tracker'!$A$3:$F$49,6,FALSE)</f>
         <v/>
       </c>
     </row>
